--- a/Formatted Data/data_prewar.xlsx
+++ b/Formatted Data/data_prewar.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t xml:space="preserve">Municipality</t>
   </si>
@@ -69,6 +69,27 @@
   </si>
   <si>
     <t xml:space="preserve">Number of Deaths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count of Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Deaths, best estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Deaths, high estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of Deaths, low estimate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deaths per 100,000, UCDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deaths per 100,000, high, UCDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deaths per 100,000, low, UCDP</t>
   </si>
   <si>
     <t xml:space="preserve">Ethnic Dominance</t>
@@ -830,10 +851,31 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B2" t="n">
         <v>1229.40168841247</v>
@@ -889,31 +931,52 @@
       <c r="S2" t="n">
         <v>1814.0061324</v>
       </c>
-      <c r="T2" t="s">
-        <v>27</v>
+      <c r="T2" t="n">
+        <v>3</v>
       </c>
       <c r="U2" t="n">
+        <v>10</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5.11007092778448</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.11007092778448</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5.11007092778448</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB2" t="n">
         <v>19.8364314558824</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="n">
         <v>134.734112799094</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AD2" t="n">
         <v>173.524688962587</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AE2" t="n">
         <v>134.734112799094</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AF2" t="n">
         <v>19.8364314558824</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0.489210519000857</v>
+      <c r="AG2" t="n">
+        <v>0.489210457923279</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B3" t="n">
         <v>189.484539258456</v>
@@ -969,31 +1032,52 @@
       <c r="S3" t="n">
         <v>292.000744</v>
       </c>
-      <c r="T3" t="s">
-        <v>29</v>
+      <c r="T3" t="n">
+        <v>14</v>
       </c>
       <c r="U3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>18</v>
+      </c>
+      <c r="X3" t="n">
+        <v>67.6946220383603</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>67.6946220383603</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>67.6946220383603</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3" t="n">
         <v>50.4139760769212</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AC3" t="n">
         <v>41.2948617300077</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AD3" t="n">
         <v>89.5244225989171</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AE3" t="n">
         <v>41.2948617300077</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AF3" t="n">
         <v>41.2948617300077</v>
       </c>
-      <c r="Z3" t="n">
-        <v>12.102796968495</v>
+      <c r="AG3" t="n">
+        <v>12.1027945745981</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B4" t="n">
         <v>729.425767613888</v>
@@ -1049,31 +1133,52 @@
       <c r="S4" t="n">
         <v>1547.0007916</v>
       </c>
-      <c r="T4" t="s">
-        <v>27</v>
+      <c r="T4" t="n">
+        <v>451</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2623</v>
       </c>
       <c r="V4" t="n">
+        <v>3009</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2532</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3708.36396539049</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>4254.08584516202</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3579.70932534072</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
         <v>223.654151343579</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AD4" t="n">
         <v>247.391952595174</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AE4" t="n">
         <v>223.654151343579</v>
       </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>12.0557923660654</v>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12.0557963274356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B5" t="n">
         <v>734.021844185727</v>
@@ -1129,31 +1234,52 @@
       <c r="S5" t="n">
         <v>1040.002324</v>
       </c>
-      <c r="T5" t="s">
-        <v>27</v>
+      <c r="T5" t="n">
+        <v>1</v>
       </c>
       <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03105538829546</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.03105538829546</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.03105538829546</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.480586128179609</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
         <v>113.967565325879</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B6" t="n">
         <v>667.126757887924</v>
@@ -1209,31 +1335,52 @@
       <c r="S6" t="n">
         <v>101.9998656</v>
       </c>
-      <c r="T6" t="s">
-        <v>27</v>
+      <c r="T6" t="n">
+        <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB6" t="n">
         <v>14.9209869581118</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AC6" t="n">
         <v>71.0829731124346</v>
       </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>14.3138922654157</v>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>14.313891274085</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B7" t="n">
         <v>543.445283790377</v>
@@ -1289,31 +1436,52 @@
       <c r="S7" t="n">
         <v>277.0013052</v>
       </c>
-      <c r="T7" t="s">
-        <v>27</v>
+      <c r="T7" t="n">
+        <v>5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="V7" t="n">
+        <v>115</v>
+      </c>
+      <c r="W7" t="n">
+        <v>58</v>
+      </c>
+      <c r="X7" t="n">
+        <v>183.50946022907</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>363.854964247295</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>183.50946022907</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
         <v>150.661110563847</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AD7" t="n">
         <v>232.085636496837</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AE7" t="n">
         <v>150.661110563847</v>
       </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>23.398376354081</v>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23.3983769847973</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
         <v>800.902679028832</v>
@@ -1369,31 +1537,52 @@
       <c r="S8" t="n">
         <v>598.000754</v>
       </c>
-      <c r="T8" t="s">
-        <v>27</v>
+      <c r="T8" t="n">
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V8" t="n">
+        <v>11</v>
+      </c>
+      <c r="W8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X8" t="n">
+        <v>18.3412812218628</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>18.3412812218628</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>15.0065028178878</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
         <v>121.055631772094</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AD8" t="n">
         <v>202.928202353462</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AE8" t="n">
         <v>121.055631772095</v>
       </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>26.595663757215</v>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>26.5956651887262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
         <v>840.024431633415</v>
@@ -1449,31 +1638,52 @@
       <c r="S9" t="n">
         <v>1314.99936</v>
       </c>
-      <c r="T9" t="s">
-        <v>27</v>
+      <c r="T9" t="n">
+        <v>257</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>803</v>
       </c>
       <c r="V9" t="n">
+        <v>1055</v>
+      </c>
+      <c r="W9" t="n">
+        <v>794</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1376.88614540466</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1808.98491083676</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1361.45404663923</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
         <v>205.780654658643</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AD9" t="n">
         <v>249.009920869855</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AE9" t="n">
         <v>205.780654658643</v>
       </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B10" t="n">
         <v>245.710390565321</v>
@@ -1529,31 +1739,52 @@
       <c r="S10" t="n">
         <v>643.9997148</v>
       </c>
-      <c r="T10" t="s">
-        <v>27</v>
+      <c r="T10" t="n">
+        <v>137</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>808</v>
       </c>
       <c r="V10" t="n">
+        <v>837</v>
+      </c>
+      <c r="W10" t="n">
+        <v>808</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2366.86390532544</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2451.81322866014</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2366.86390532544</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>60.458367806546</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AD10" t="n">
         <v>172.923988007989</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AE10" t="n">
         <v>60.458367806546</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
         <v>577.381926239548</v>
@@ -1609,31 +1840,52 @@
       <c r="S11" t="n">
         <v>669.998199</v>
       </c>
-      <c r="T11" t="s">
-        <v>27</v>
+      <c r="T11" t="n">
+        <v>63</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="V11" t="n">
+        <v>153</v>
+      </c>
+      <c r="W11" t="n">
+        <v>151</v>
+      </c>
+      <c r="X11" t="n">
+        <v>367.214688587543</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>367.214688587543</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>362.414496579863</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>180.556751965929</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AD11" t="n">
         <v>247.184597344818</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AE11" t="n">
         <v>180.556751965929</v>
       </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B12" t="n">
         <v>838.882395200677</v>
@@ -1689,31 +1941,52 @@
       <c r="S12" t="n">
         <v>373.9995441</v>
       </c>
-      <c r="T12" t="s">
-        <v>27</v>
+      <c r="T12" t="n">
+        <v>8</v>
       </c>
       <c r="U12" t="n">
+        <v>194</v>
+      </c>
+      <c r="V12" t="n">
+        <v>289</v>
+      </c>
+      <c r="W12" t="n">
+        <v>194</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1241.91793099033</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1850.07361884642</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1241.91793099033</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2.94492251033371</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AC12" t="n">
         <v>188.179212256151</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AD12" t="n">
         <v>209.802832849761</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AE12" t="n">
         <v>188.179212256151</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AF12" t="n">
         <v>2.94492251033371</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AG12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B13" t="n">
         <v>192.703975582829</v>
@@ -1769,31 +2042,52 @@
       <c r="S13" t="n">
         <v>622.001344</v>
       </c>
-      <c r="T13" t="s">
-        <v>27</v>
+      <c r="T13" t="n">
+        <v>36</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="V13" t="n">
+        <v>106</v>
+      </c>
+      <c r="W13" t="n">
+        <v>106</v>
+      </c>
+      <c r="X13" t="n">
+        <v>321.601941747573</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>321.601941747573</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>321.601941747573</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
         <v>28.3925912505513</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AD13" t="n">
         <v>155.340100821355</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AE13" t="n">
         <v>28.3925912505513</v>
       </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B14" t="n">
         <v>771.215071192192</v>
@@ -1849,31 +2143,52 @@
       <c r="S14" t="n">
         <v>177.0001981</v>
       </c>
-      <c r="T14" t="s">
-        <v>29</v>
+      <c r="T14" t="n">
+        <v>36</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="V14" t="n">
+        <v>343</v>
+      </c>
+      <c r="W14" t="n">
+        <v>116</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1395.74058476718</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4127.0605221995</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1395.74058476718</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
         <v>194.661520700844</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AD14" t="n">
         <v>182.190510121757</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AE14" t="n">
         <v>182.190510121757</v>
       </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>12.0541946790134</v>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.0541979969418</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B15" t="n">
         <v>257.129545162228</v>
@@ -1929,31 +2244,52 @@
       <c r="S15" t="n">
         <v>3604.0005047</v>
       </c>
-      <c r="T15" t="s">
-        <v>27</v>
+      <c r="T15" t="n">
+        <v>75</v>
       </c>
       <c r="U15" t="n">
+        <v>576</v>
+      </c>
+      <c r="V15" t="n">
+        <v>666</v>
+      </c>
+      <c r="W15" t="n">
+        <v>576</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1713.31687438651</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1981.0226360094</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1713.31687438651</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15" t="n">
         <v>66.9986093475407</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
         <v>61.7122312277863</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>22.3136396855869</v>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>22.3136439204384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B16" t="n">
         <v>65.0002448772612</v>
@@ -2009,31 +2345,52 @@
       <c r="S16" t="n">
         <v>263.9993967</v>
       </c>
-      <c r="T16" t="s">
-        <v>29</v>
+      <c r="T16" t="n">
+        <v>6</v>
       </c>
       <c r="U16" t="n">
+        <v>8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>46.1973782987815</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>46.1973782987815</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>46.1973782987815</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB16" t="n">
         <v>93.7896398785743</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AC16" t="n">
         <v>69.3387220897303</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AD16" t="n">
         <v>70.7302526565159</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AE16" t="n">
         <v>69.3387220897303</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AF16" t="n">
         <v>69.3387220897303</v>
       </c>
-      <c r="Z16" t="n">
-        <v>13.6910068617474</v>
+      <c r="AG16" t="n">
+        <v>13.6910082039664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B17" t="n">
         <v>471.638202483051</v>
@@ -2089,31 +2446,52 @@
       <c r="S17" t="n">
         <v>1657.9992297</v>
       </c>
-      <c r="T17" t="s">
-        <v>27</v>
+      <c r="T17" t="n">
+        <v>406</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4981</v>
       </c>
       <c r="V17" t="n">
+        <v>5059</v>
+      </c>
+      <c r="W17" t="n">
+        <v>4840</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5684.32104260102</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>5773.33470277426</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5523.41173382633</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.01880620009917</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AD17" t="n">
         <v>131.896968879258</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AE17" t="n">
         <v>2.0188062000991</v>
       </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B18" t="n">
         <v>360.282341445597</v>
@@ -2169,31 +2547,52 @@
       <c r="S18" t="n">
         <v>797.9992021</v>
       </c>
-      <c r="T18" t="s">
-        <v>27</v>
+      <c r="T18" t="n">
+        <v>99</v>
       </c>
       <c r="U18" t="n">
+        <v>697</v>
+      </c>
+      <c r="V18" t="n">
+        <v>704</v>
+      </c>
+      <c r="W18" t="n">
+        <v>684</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1486.48936850861</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1501.41824308473</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1458.76431572437</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB18" t="n">
         <v>44.1827287667677</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AC18" t="n">
         <v>125.575376911153</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AD18" t="n">
         <v>122.02394387656</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AE18" t="n">
         <v>122.02394387656</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AF18" t="n">
         <v>44.1827287667677</v>
       </c>
-      <c r="Z18" t="n">
-        <v>7.05263805798835</v>
+      <c r="AG18" t="n">
+        <v>7.05263538742283</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B19" t="n">
         <v>157.151887154685</v>
@@ -2249,31 +2648,52 @@
       <c r="S19" t="n">
         <v>364.0003353</v>
       </c>
-      <c r="T19" t="s">
-        <v>27</v>
+      <c r="T19" t="n">
+        <v>60</v>
       </c>
       <c r="U19" t="n">
+        <v>228</v>
+      </c>
+      <c r="V19" t="n">
+        <v>249</v>
+      </c>
+      <c r="W19" t="n">
+        <v>223</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1207.69108533291</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1318.92579056094</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1181.20663170719</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB19" t="n">
         <v>73.438128751261</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AC19" t="n">
         <v>92.8961639582762</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AD19" t="n">
         <v>95.7975821287272</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AE19" t="n">
         <v>92.8961639582762</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AF19" t="n">
         <v>73.438128751261</v>
       </c>
-      <c r="Z19" t="n">
-        <v>26.5197690711577</v>
+      <c r="AG19" t="n">
+        <v>26.5197703728574</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B20" t="n">
         <v>310.582369389773</v>
@@ -2329,31 +2749,52 @@
       <c r="S20" t="n">
         <v>917.0019353</v>
       </c>
-      <c r="T20" t="s">
-        <v>29</v>
+      <c r="T20" t="n">
+        <v>126</v>
       </c>
       <c r="U20" t="n">
+        <v>342</v>
+      </c>
+      <c r="V20" t="n">
+        <v>527</v>
+      </c>
+      <c r="W20" t="n">
+        <v>339</v>
+      </c>
+      <c r="X20" t="n">
+        <v>539.355611979372</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>831.112302669968</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>534.624422400606</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB20" t="n">
         <v>0.549014526735777</v>
       </c>
-      <c r="V20" t="n">
+      <c r="AC20" t="n">
         <v>229.819023433374</v>
       </c>
-      <c r="W20" t="n">
+      <c r="AD20" t="n">
         <v>275.853401495909</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AE20" t="n">
         <v>229.819023433374</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AF20" t="n">
         <v>0.549014526735777</v>
       </c>
-      <c r="Z20" t="n">
-        <v>9.82906983320066</v>
+      <c r="AG20" t="n">
+        <v>9.82907209239593</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B21" t="n">
         <v>533.36134036364</v>
@@ -2409,31 +2850,52 @@
       <c r="S21" t="n">
         <v>944.9988321</v>
       </c>
-      <c r="T21" t="s">
-        <v>27</v>
+      <c r="T21" t="n">
+        <v>86</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="V21" t="n">
+        <v>587</v>
+      </c>
+      <c r="W21" t="n">
+        <v>476</v>
+      </c>
+      <c r="X21" t="n">
+        <v>986.032678928641</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1039.14036361061</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>842.641930287313</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
         <v>69.1052830042277</v>
       </c>
-      <c r="W21" t="n">
+      <c r="AD21" t="n">
         <v>159.272075382624</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AE21" t="n">
         <v>69.1052830042277</v>
       </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7.24967156706507</v>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>7.24966694255321</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B22" t="n">
         <v>700.965790155761</v>
@@ -2489,31 +2951,52 @@
       <c r="S22" t="n">
         <v>2315.9973807</v>
       </c>
-      <c r="T22" t="s">
-        <v>27</v>
+      <c r="T22" t="n">
+        <v>368</v>
       </c>
       <c r="U22" t="n">
+        <v>1270</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1549</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1220</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1238.43235916489</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1510.4974207452</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1189.67517967021</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB22" t="n">
         <v>9.85160030893012</v>
       </c>
-      <c r="V22" t="n">
+      <c r="AC22" t="n">
         <v>58.238237186317</v>
       </c>
-      <c r="W22" t="n">
+      <c r="AD22" t="n">
         <v>139.726875786283</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AE22" t="n">
         <v>58.238237186317</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AF22" t="n">
         <v>9.85160030893012</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AG22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B23" t="n">
         <v>332.821968347177</v>
@@ -2569,31 +3052,52 @@
       <c r="S23" t="n">
         <v>282.0007424</v>
       </c>
-      <c r="T23" t="s">
-        <v>27</v>
+      <c r="T23" t="n">
+        <v>46</v>
       </c>
       <c r="U23" t="n">
+        <v>141</v>
+      </c>
+      <c r="V23" t="n">
+        <v>441</v>
+      </c>
+      <c r="W23" t="n">
+        <v>106</v>
+      </c>
+      <c r="X23" t="n">
+        <v>574.478487614081</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1796.77314211213</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>431.877444589309</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23" t="n">
         <v>46.2107922191538</v>
       </c>
-      <c r="V23" t="n">
+      <c r="AC23" t="n">
         <v>130.023561960953</v>
       </c>
-      <c r="W23" t="n">
+      <c r="AD23" t="n">
         <v>135.304027524578</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AE23" t="n">
         <v>130.023561960953</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AF23" t="n">
         <v>46.2107922191538</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AG23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B24" t="n">
         <v>944.369726706419</v>
@@ -2649,31 +3153,52 @@
       <c r="S24" t="n">
         <v>142.000229</v>
       </c>
-      <c r="T24" t="s">
-        <v>29</v>
+      <c r="T24" t="n">
+        <v>6</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V24" t="n">
+        <v>20</v>
+      </c>
+      <c r="W24" t="n">
+        <v>20</v>
+      </c>
+      <c r="X24" t="n">
+        <v>116.781501810113</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>116.781501810113</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>116.781501810113</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
         <v>188.947379380102</v>
       </c>
-      <c r="W24" t="n">
+      <c r="AD24" t="n">
         <v>196.355353516385</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AE24" t="n">
         <v>188.947379380102</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B25" t="n">
         <v>304.550316585878</v>
@@ -2729,31 +3254,52 @@
       <c r="S25" t="n">
         <v>298.0000632</v>
       </c>
-      <c r="T25" t="s">
-        <v>27</v>
+      <c r="T25" t="n">
+        <v>87</v>
       </c>
       <c r="U25" t="n">
+        <v>316</v>
+      </c>
+      <c r="V25" t="n">
+        <v>316</v>
+      </c>
+      <c r="W25" t="n">
+        <v>274</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1939.12616593029</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1939.12616593029</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1681.3942071674</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB25" t="n">
         <v>61.0523526795943</v>
       </c>
-      <c r="V25" t="n">
+      <c r="AC25" t="n">
         <v>98.6095916165155</v>
       </c>
-      <c r="W25" t="n">
+      <c r="AD25" t="n">
         <v>86.0497035089757</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AE25" t="n">
         <v>86.0497035089755</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AF25" t="n">
         <v>61.0523526795943</v>
       </c>
-      <c r="Z25" t="n">
-        <v>29.0596431347924</v>
+      <c r="AG25" t="n">
+        <v>29.0596397295145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B26" t="n">
         <v>1192.54583494142</v>
@@ -2809,31 +3355,52 @@
       <c r="S26" t="n">
         <v>2804.998581</v>
       </c>
-      <c r="T26" t="s">
-        <v>27</v>
+      <c r="T26" t="n">
+        <v>16</v>
       </c>
       <c r="U26" t="n">
+        <v>103</v>
+      </c>
+      <c r="V26" t="n">
+        <v>104</v>
+      </c>
+      <c r="W26" t="n">
+        <v>103</v>
+      </c>
+      <c r="X26" t="n">
+        <v>254.239379952114</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>256.707723446795</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>254.239379952114</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB26" t="n">
         <v>75.7769388906497</v>
       </c>
-      <c r="V26" t="n">
+      <c r="AC26" t="n">
         <v>13.0517873310174</v>
       </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B27" t="n">
         <v>737.165072059161</v>
@@ -2889,31 +3456,52 @@
       <c r="S27" t="n">
         <v>364.0000656</v>
       </c>
-      <c r="T27" t="s">
-        <v>27</v>
+      <c r="T27" t="n">
+        <v>0</v>
       </c>
       <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB27" t="n">
         <v>44.4748673064484</v>
       </c>
-      <c r="V27" t="n">
+      <c r="AC27" t="n">
         <v>45.2547568154745</v>
       </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>17.2453615128123</v>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>17.2453609360726</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B28" t="n">
         <v>1059.59273552269</v>
@@ -2969,31 +3557,52 @@
       <c r="S28" t="n">
         <v>171.000347</v>
       </c>
-      <c r="T28" t="s">
-        <v>29</v>
+      <c r="T28" t="n">
+        <v>18</v>
       </c>
       <c r="U28" t="n">
+        <v>64</v>
+      </c>
+      <c r="V28" t="n">
+        <v>78</v>
+      </c>
+      <c r="W28" t="n">
+        <v>64</v>
+      </c>
+      <c r="X28" t="n">
+        <v>508.218851743032</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>619.39172556182</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>508.218851743032</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB28" t="n">
         <v>12.8458239251246</v>
       </c>
-      <c r="V28" t="n">
+      <c r="AC28" t="n">
         <v>164.783071437611</v>
       </c>
-      <c r="W28" t="n">
+      <c r="AD28" t="n">
         <v>148.15076777427</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AE28" t="n">
         <v>148.150767774269</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AF28" t="n">
         <v>12.8458239251246</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AG28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B29" t="n">
         <v>395.86891682019</v>
@@ -3049,31 +3658,52 @@
       <c r="S29" t="n">
         <v>1636.9992505</v>
       </c>
-      <c r="T29" t="s">
-        <v>27</v>
+      <c r="T29" t="n">
+        <v>371</v>
       </c>
       <c r="U29" t="n">
+        <v>2474</v>
+      </c>
+      <c r="V29" t="n">
+        <v>2942</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2221</v>
+      </c>
+      <c r="X29" t="n">
+        <v>6584.515476539</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>7830.09075666037</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5911.15960929391</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB29" t="n">
         <v>106.693303690715</v>
       </c>
-      <c r="V29" t="n">
+      <c r="AC29" t="n">
         <v>9.8499827117942</v>
       </c>
-      <c r="W29" t="n">
+      <c r="AD29" t="n">
         <v>0.377649652200105</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AE29" t="n">
         <v>0.377649652198766</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AF29" t="n">
         <v>0.377649652198766</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AG29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B30" t="n">
         <v>438.298722305351</v>
@@ -3129,31 +3759,52 @@
       <c r="S30" t="n">
         <v>547.9989944</v>
       </c>
-      <c r="T30" t="s">
-        <v>27</v>
+      <c r="T30" t="n">
+        <v>216</v>
       </c>
       <c r="U30" t="n">
+        <v>749</v>
+      </c>
+      <c r="V30" t="n">
+        <v>749</v>
+      </c>
+      <c r="W30" t="n">
+        <v>698</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2974.46487431</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2974.46487431</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2771.93121798181</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30" t="n">
         <v>42.7432195984159</v>
       </c>
-      <c r="V30" t="n">
+      <c r="AC30" t="n">
         <v>111.662088503682</v>
       </c>
-      <c r="W30" t="n">
+      <c r="AD30" t="n">
         <v>96.5303805571575</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AE30" t="n">
         <v>96.5303805571573</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AF30" t="n">
         <v>42.7432195984159</v>
       </c>
-      <c r="Z30" t="n">
-        <v>22.1546954744718</v>
+      <c r="AG30" t="n">
+        <v>22.1546949901459</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B31" t="n">
         <v>444.582286767581</v>
@@ -3209,31 +3860,52 @@
       <c r="S31" t="n">
         <v>898.9985347</v>
       </c>
-      <c r="T31" t="s">
-        <v>27</v>
+      <c r="T31" t="n">
+        <v>243</v>
       </c>
       <c r="U31" t="n">
+        <v>998</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1009</v>
+      </c>
+      <c r="W31" t="n">
+        <v>997</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1763.84298616143</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1783.28414131952</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1762.07560841979</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB31" t="n">
         <v>7.31354678377015</v>
       </c>
-      <c r="V31" t="n">
+      <c r="AC31" t="n">
         <v>25.9318555306303</v>
       </c>
-      <c r="W31" t="n">
+      <c r="AD31" t="n">
         <v>139.756326904752</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AE31" t="n">
         <v>25.9318555306303</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AF31" t="n">
         <v>7.31354678377015</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AG31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B32" t="n">
         <v>433.193496135842</v>
@@ -3289,31 +3961,52 @@
       <c r="S32" t="n">
         <v>484.9993278</v>
       </c>
-      <c r="T32" t="s">
-        <v>27</v>
+      <c r="T32" t="n">
+        <v>32</v>
       </c>
       <c r="U32" t="n">
+        <v>52</v>
+      </c>
+      <c r="V32" t="n">
+        <v>55</v>
+      </c>
+      <c r="W32" t="n">
+        <v>52</v>
+      </c>
+      <c r="X32" t="n">
+        <v>87.9358744546285</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>93.009097980857</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>87.9358744546285</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB32" t="n">
         <v>28.4495127591022</v>
       </c>
-      <c r="V32" t="n">
+      <c r="AC32" t="n">
         <v>44.8725637166345</v>
       </c>
-      <c r="W32" t="n">
+      <c r="AD32" t="n">
         <v>124.418037444266</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AE32" t="n">
         <v>44.8725637166345</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AF32" t="n">
         <v>28.4495127591022</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AG32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B33" t="n">
         <v>166.552375907341</v>
@@ -3369,31 +4062,52 @@
       <c r="S33" t="n">
         <v>34.000103</v>
       </c>
-      <c r="T33" t="s">
-        <v>29</v>
+      <c r="T33" t="n">
+        <v>0</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
         <v>137.172849591456</v>
       </c>
-      <c r="W33" t="n">
+      <c r="AD33" t="n">
         <v>88.9953298796267</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AE33" t="n">
         <v>88.9953298796267</v>
       </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>35.4441280536292</v>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>35.4441269921645</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B34" t="n">
         <v>285.013282395347</v>
@@ -3449,31 +4163,52 @@
       <c r="S34" t="n">
         <v>635.00074</v>
       </c>
-      <c r="T34" t="s">
-        <v>27</v>
+      <c r="T34" t="n">
+        <v>6</v>
       </c>
       <c r="U34" t="n">
+        <v>79</v>
+      </c>
+      <c r="V34" t="n">
+        <v>79</v>
+      </c>
+      <c r="W34" t="n">
+        <v>79</v>
+      </c>
+      <c r="X34" t="n">
+        <v>326.446280991736</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>326.446280991736</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>326.446280991736</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB34" t="n">
         <v>64.6145112623306</v>
       </c>
-      <c r="V34" t="n">
+      <c r="AC34" t="n">
         <v>76.7872821776496</v>
       </c>
-      <c r="W34" t="n">
+      <c r="AD34" t="n">
         <v>58.0152222793452</v>
       </c>
-      <c r="X34" t="n">
+      <c r="AE34" t="n">
         <v>58.0152222793452</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AF34" t="n">
         <v>58.0152222793452</v>
       </c>
-      <c r="Z34" t="n">
-        <v>5.0003331756048</v>
+      <c r="AG34" t="n">
+        <v>5.00033287471526</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B35" t="n">
         <v>358.002135904775</v>
@@ -3529,31 +4264,52 @@
       <c r="S35" t="n">
         <v>153.0001308</v>
       </c>
-      <c r="T35" t="s">
-        <v>27</v>
+      <c r="T35" t="n">
+        <v>0</v>
       </c>
       <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB35" t="n">
         <v>76.0651663846019</v>
       </c>
-      <c r="V35" t="n">
+      <c r="AC35" t="n">
         <v>5.53343627850065</v>
       </c>
-      <c r="W35" t="n">
+      <c r="AD35" t="n">
         <v>45.4520848349218</v>
       </c>
-      <c r="X35" t="n">
+      <c r="AE35" t="n">
         <v>5.53343627850065</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AF35" t="n">
         <v>5.53343627850065</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AG35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B36" t="n">
         <v>157.923142766565</v>
@@ -3609,31 +4365,52 @@
       <c r="S36" t="n">
         <v>1654.0009957</v>
       </c>
-      <c r="T36" t="s">
-        <v>27</v>
+      <c r="T36" t="n">
+        <v>21</v>
       </c>
       <c r="U36" t="n">
+        <v>185</v>
+      </c>
+      <c r="V36" t="n">
+        <v>188</v>
+      </c>
+      <c r="W36" t="n">
+        <v>122</v>
+      </c>
+      <c r="X36" t="n">
+        <v>272.311111765312</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>276.726967631777</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>179.578138569557</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB36" t="n">
         <v>81.969421068352</v>
       </c>
-      <c r="V36" t="n">
+      <c r="AC36" t="n">
         <v>67.6082795219309</v>
       </c>
-      <c r="W36" t="n">
+      <c r="AD36" t="n">
         <v>50.6726453057755</v>
       </c>
-      <c r="X36" t="n">
+      <c r="AE36" t="n">
         <v>50.6726453057753</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AF36" t="n">
         <v>50.6726453057753</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AG36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B37" t="n">
         <v>312.50361492967</v>
@@ -3689,31 +4466,52 @@
       <c r="S37" t="n">
         <v>529.9997984</v>
       </c>
-      <c r="T37" t="s">
-        <v>27</v>
+      <c r="T37" t="n">
+        <v>28</v>
       </c>
       <c r="U37" t="n">
+        <v>77</v>
+      </c>
+      <c r="V37" t="n">
+        <v>79</v>
+      </c>
+      <c r="W37" t="n">
+        <v>77</v>
+      </c>
+      <c r="X37" t="n">
+        <v>305.749682337992</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>313.69123252859</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>305.749682337992</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB37" t="n">
         <v>87.926576411056</v>
       </c>
-      <c r="V37" t="n">
+      <c r="AC37" t="n">
         <v>46.7493328813668</v>
       </c>
-      <c r="W37" t="n">
+      <c r="AD37" t="n">
         <v>53.9223490730088</v>
       </c>
-      <c r="X37" t="n">
+      <c r="AE37" t="n">
         <v>46.7493328813668</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AF37" t="n">
         <v>46.7493328813668</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AG37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B38" t="n">
         <v>324.184713312212</v>
@@ -3769,31 +4567,52 @@
       <c r="S38" t="n">
         <v>277.0001115</v>
       </c>
-      <c r="T38" t="s">
-        <v>29</v>
+      <c r="T38" t="n">
+        <v>83</v>
       </c>
       <c r="U38" t="n">
+        <v>322</v>
+      </c>
+      <c r="V38" t="n">
+        <v>322</v>
+      </c>
+      <c r="W38" t="n">
+        <v>322</v>
+      </c>
+      <c r="X38" t="n">
+        <v>2537.23110865968</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2537.23110865968</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2537.23110865968</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB38" t="n">
         <v>25.3319417956366</v>
       </c>
-      <c r="V38" t="n">
+      <c r="AC38" t="n">
         <v>105.68855187145</v>
       </c>
-      <c r="W38" t="n">
+      <c r="AD38" t="n">
         <v>74.4482589363525</v>
       </c>
-      <c r="X38" t="n">
+      <c r="AE38" t="n">
         <v>74.4482589363524</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AF38" t="n">
         <v>25.3319417956366</v>
       </c>
-      <c r="Z38" t="n">
-        <v>13.9077150606168</v>
+      <c r="AG38" t="n">
+        <v>13.9077114183943</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B39" t="n">
         <v>376.666528108197</v>
@@ -3849,31 +4668,52 @@
       <c r="S39" t="n">
         <v>698.9992163</v>
       </c>
-      <c r="T39" t="s">
-        <v>27</v>
+      <c r="T39" t="n">
+        <v>134</v>
       </c>
       <c r="U39" t="n">
+        <v>775</v>
+      </c>
+      <c r="V39" t="n">
+        <v>778</v>
+      </c>
+      <c r="W39" t="n">
+        <v>736</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1721.9543626547</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1728.61999244562</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1635.30117537272</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB39" t="n">
         <v>57.564300873638</v>
       </c>
-      <c r="V39" t="n">
+      <c r="AC39" t="n">
         <v>133.90276158664</v>
       </c>
-      <c r="W39" t="n">
+      <c r="AD39" t="n">
         <v>145.539494159701</v>
       </c>
-      <c r="X39" t="n">
+      <c r="AE39" t="n">
         <v>133.90276158664</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AF39" t="n">
         <v>57.564300873638</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AG39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B40" t="n">
         <v>483.998701392131</v>
@@ -3929,31 +4769,52 @@
       <c r="S40" t="n">
         <v>477.001725</v>
       </c>
-      <c r="T40" t="s">
-        <v>27</v>
+      <c r="T40" t="n">
+        <v>26</v>
       </c>
       <c r="U40" t="n">
+        <v>167</v>
+      </c>
+      <c r="V40" t="n">
+        <v>167</v>
+      </c>
+      <c r="W40" t="n">
+        <v>167</v>
+      </c>
+      <c r="X40" t="n">
+        <v>298.480786416443</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>298.480786416443</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>298.480786416443</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB40" t="n">
         <v>72.8457691891865</v>
       </c>
-      <c r="V40" t="n">
+      <c r="AC40" t="n">
         <v>59.8866565843964</v>
       </c>
-      <c r="W40" t="n">
+      <c r="AD40" t="n">
         <v>84.15141756894</v>
       </c>
-      <c r="X40" t="n">
+      <c r="AE40" t="n">
         <v>59.8866565843964</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AF40" t="n">
         <v>59.8866565843964</v>
       </c>
-      <c r="Z40" t="n">
-        <v>20.1511386162538</v>
+      <c r="AG40" t="n">
+        <v>20.1511399856483</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B41" t="n">
         <v>267.821341133633</v>
@@ -4009,31 +4870,52 @@
       <c r="S41" t="n">
         <v>660.0010549</v>
       </c>
-      <c r="T41" t="s">
-        <v>29</v>
+      <c r="T41" t="n">
+        <v>130</v>
       </c>
       <c r="U41" t="n">
+        <v>456</v>
+      </c>
+      <c r="V41" t="n">
+        <v>561</v>
+      </c>
+      <c r="W41" t="n">
+        <v>423</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1090.67425673898</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1341.81635533019</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1011.74388289603</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB41" t="n">
         <v>34.9129130078874</v>
       </c>
-      <c r="V41" t="n">
+      <c r="AC41" t="n">
         <v>5.23270425342291</v>
       </c>
-      <c r="W41" t="n">
+      <c r="AD41" t="n">
         <v>89.1209122358853</v>
       </c>
-      <c r="X41" t="n">
+      <c r="AE41" t="n">
         <v>5.23270425342291</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="AF41" t="n">
         <v>5.23270425342291</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="AG41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B42" t="n">
         <v>808.54685712195</v>
@@ -4089,31 +4971,52 @@
       <c r="S42" t="n">
         <v>269.999951</v>
       </c>
-      <c r="T42" t="s">
-        <v>27</v>
+      <c r="T42" t="n">
+        <v>83</v>
       </c>
       <c r="U42" t="n">
+        <v>279</v>
+      </c>
+      <c r="V42" t="n">
+        <v>538</v>
+      </c>
+      <c r="W42" t="n">
+        <v>236</v>
+      </c>
+      <c r="X42" t="n">
+        <v>5978.14441825584</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>11527.7480179987</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>5056.78165845297</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB42" t="n">
         <v>51.5717207625457</v>
       </c>
-      <c r="V42" t="n">
+      <c r="AC42" t="n">
         <v>46.4084999659415</v>
       </c>
-      <c r="W42" t="n">
+      <c r="AD42" t="n">
         <v>14.2640321179829</v>
       </c>
-      <c r="X42" t="n">
+      <c r="AE42" t="n">
         <v>14.2640321179827</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="AF42" t="n">
         <v>14.2640321179827</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="AG42" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B43" t="n">
         <v>180.117831298126</v>
@@ -4169,31 +5072,52 @@
       <c r="S43" t="n">
         <v>429.0004068</v>
       </c>
-      <c r="T43" t="s">
-        <v>27</v>
+      <c r="T43" t="n">
+        <v>116</v>
       </c>
       <c r="U43" t="n">
+        <v>324</v>
+      </c>
+      <c r="V43" t="n">
+        <v>379</v>
+      </c>
+      <c r="W43" t="n">
+        <v>324</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1340.83760966727</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1568.44893229598</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>1340.83760966727</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB43" t="n">
         <v>72.2814587788184</v>
       </c>
-      <c r="V43" t="n">
+      <c r="AC43" t="n">
         <v>86.6898196201546</v>
       </c>
-      <c r="W43" t="n">
+      <c r="AD43" t="n">
         <v>70.8168739479438</v>
       </c>
-      <c r="X43" t="n">
+      <c r="AE43" t="n">
         <v>70.8168739479436</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="AF43" t="n">
         <v>70.8168739479436</v>
       </c>
-      <c r="Z43" t="n">
-        <v>14.0171508187783</v>
+      <c r="AG43" t="n">
+        <v>14.0171494686207</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B44" t="n">
         <v>314.055808172675</v>
@@ -4249,31 +5173,52 @@
       <c r="S44" t="n">
         <v>204.000615</v>
       </c>
-      <c r="T44" t="s">
-        <v>27</v>
+      <c r="T44" t="n">
+        <v>23</v>
       </c>
       <c r="U44" t="n">
+        <v>57</v>
+      </c>
+      <c r="V44" t="n">
+        <v>57</v>
+      </c>
+      <c r="W44" t="n">
+        <v>54</v>
+      </c>
+      <c r="X44" t="n">
+        <v>354.698195395146</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>354.698195395146</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>336.029869321718</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB44" t="n">
         <v>57.2869520682386</v>
       </c>
-      <c r="V44" t="n">
+      <c r="AC44" t="n">
         <v>24.1102728442288</v>
       </c>
-      <c r="W44" t="n">
+      <c r="AD44" t="n">
         <v>70.3913495631194</v>
       </c>
-      <c r="X44" t="n">
+      <c r="AE44" t="n">
         <v>24.1102728442287</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="AF44" t="n">
         <v>24.1102728442287</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="AG44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B45" t="n">
         <v>873.923447015203</v>
@@ -4329,31 +5274,52 @@
       <c r="S45" t="n">
         <v>1213.9997707</v>
       </c>
-      <c r="T45" t="s">
-        <v>27</v>
+      <c r="T45" t="n">
+        <v>33</v>
       </c>
       <c r="U45" t="n">
+        <v>397</v>
+      </c>
+      <c r="V45" t="n">
+        <v>397</v>
+      </c>
+      <c r="W45" t="n">
+        <v>349</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1061.75282822069</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1061.75282822069</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>933.379690299805</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB45" t="n">
         <v>33.223332674935</v>
       </c>
-      <c r="V45" t="n">
+      <c r="AC45" t="n">
         <v>162.217611800506</v>
       </c>
-      <c r="W45" t="n">
+      <c r="AD45" t="n">
         <v>187.175240179071</v>
       </c>
-      <c r="X45" t="n">
+      <c r="AE45" t="n">
         <v>162.217611800506</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AF45" t="n">
         <v>33.223332674935</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AG45" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B46" t="n">
         <v>1065.05893496374</v>
@@ -4409,31 +5375,52 @@
       <c r="S46" t="n">
         <v>987.0005076</v>
       </c>
-      <c r="T46" t="s">
-        <v>27</v>
+      <c r="T46" t="n">
+        <v>119</v>
       </c>
       <c r="U46" t="n">
+        <v>403</v>
+      </c>
+      <c r="V46" t="n">
+        <v>546</v>
+      </c>
+      <c r="W46" t="n">
+        <v>381</v>
+      </c>
+      <c r="X46" t="n">
+        <v>918.455718127535</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1244.35936004376</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>868.31669629427</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB46" t="n">
         <v>44.7493675808426</v>
       </c>
-      <c r="V46" t="n">
+      <c r="AC46" t="n">
         <v>69.7906090719696</v>
       </c>
-      <c r="W46" t="n">
+      <c r="AD46" t="n">
         <v>39.4687067637603</v>
       </c>
-      <c r="X46" t="n">
+      <c r="AE46" t="n">
         <v>39.4687067637601</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AF46" t="n">
         <v>39.4687067637601</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="AG46" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B47" t="n">
         <v>642.329674065164</v>
@@ -4489,31 +5476,52 @@
       <c r="S47" t="n">
         <v>1048.9985332</v>
       </c>
-      <c r="T47" t="s">
-        <v>27</v>
+      <c r="T47" t="n">
+        <v>1</v>
       </c>
       <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>7</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>18.9943830895721</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB47" t="n">
         <v>49.145475868072</v>
       </c>
-      <c r="V47" t="n">
+      <c r="AC47" t="n">
         <v>112.016461464685</v>
       </c>
-      <c r="W47" t="n">
+      <c r="AD47" t="n">
         <v>135.525175771732</v>
       </c>
-      <c r="X47" t="n">
+      <c r="AE47" t="n">
         <v>112.016461464685</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="AF47" t="n">
         <v>49.145475868072</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="AG47" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B48" t="n">
         <v>144.79710589861</v>
@@ -4569,31 +5577,52 @@
       <c r="S48" t="n">
         <v>110.0000213</v>
       </c>
-      <c r="T48" t="s">
-        <v>27</v>
+      <c r="T48" t="n">
+        <v>52</v>
       </c>
       <c r="U48" t="n">
+        <v>131</v>
+      </c>
+      <c r="V48" t="n">
+        <v>134</v>
+      </c>
+      <c r="W48" t="n">
+        <v>123</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1946.2189867776</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1990.78888723815</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1827.36591888278</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB48" t="n">
         <v>61.6021934402338</v>
       </c>
-      <c r="V48" t="n">
+      <c r="AC48" t="n">
         <v>90.4866376003664</v>
       </c>
-      <c r="W48" t="n">
+      <c r="AD48" t="n">
         <v>75.4624366810065</v>
       </c>
-      <c r="X48" t="n">
+      <c r="AE48" t="n">
         <v>75.4624366810063</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AF48" t="n">
         <v>61.6021934402338</v>
       </c>
-      <c r="Z48" t="n">
-        <v>18.7769723393965</v>
+      <c r="AG48" t="n">
+        <v>18.7769688822436</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B49" t="n">
         <v>592.168291611245</v>
@@ -4649,31 +5678,52 @@
       <c r="S49" t="n">
         <v>284.9996142</v>
       </c>
-      <c r="T49" t="s">
-        <v>27</v>
+      <c r="T49" t="n">
+        <v>34</v>
       </c>
       <c r="U49" t="n">
+        <v>132</v>
+      </c>
+      <c r="V49" t="n">
+        <v>132</v>
+      </c>
+      <c r="W49" t="n">
+        <v>97</v>
+      </c>
+      <c r="X49" t="n">
+        <v>1372.42669993762</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1372.42669993762</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1008.52568101476</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB49" t="n">
         <v>22.7783881549202</v>
       </c>
-      <c r="V49" t="n">
+      <c r="AC49" t="n">
         <v>143.926898724953</v>
       </c>
-      <c r="W49" t="n">
+      <c r="AD49" t="n">
         <v>120.418602681005</v>
       </c>
-      <c r="X49" t="n">
+      <c r="AE49" t="n">
         <v>120.418602681005</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="AF49" t="n">
         <v>22.7783881549202</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="AG49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B50" t="n">
         <v>401.982217946416</v>
@@ -4729,31 +5779,52 @@
       <c r="S50" t="n">
         <v>233.9992248</v>
       </c>
-      <c r="T50" t="s">
-        <v>27</v>
+      <c r="T50" t="n">
+        <v>0</v>
       </c>
       <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB50" t="n">
         <v>15.8860730724989</v>
       </c>
-      <c r="V50" t="n">
+      <c r="AC50" t="n">
         <v>117.404543008559</v>
       </c>
-      <c r="W50" t="n">
+      <c r="AD50" t="n">
         <v>182.945894254121</v>
       </c>
-      <c r="X50" t="n">
+      <c r="AE50" t="n">
         <v>117.404543008559</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AF50" t="n">
         <v>15.8860730724989</v>
       </c>
-      <c r="Z50" t="n">
-        <v>33.3616199359498</v>
+      <c r="AG50" t="n">
+        <v>33.3616181198627</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B51" t="n">
         <v>921.666260614532</v>
@@ -4809,31 +5880,52 @@
       <c r="S51" t="n">
         <v>95.9987</v>
       </c>
-      <c r="T51" t="s">
-        <v>29</v>
+      <c r="T51" t="n">
+        <v>27</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="V51" t="n">
+        <v>293</v>
+      </c>
+      <c r="W51" t="n">
+        <v>43</v>
+      </c>
+      <c r="X51" t="n">
+        <v>105.911330049261</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>721.674876847291</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>105.911330049261</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
         <v>166.051866232384</v>
       </c>
-      <c r="W51" t="n">
+      <c r="AD51" t="n">
         <v>137.243485057598</v>
       </c>
-      <c r="X51" t="n">
+      <c r="AE51" t="n">
         <v>137.243485057598</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>19.0829980077144</v>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>19.0829920385024</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B52" t="n">
         <v>333.528782412207</v>
@@ -4889,31 +5981,52 @@
       <c r="S52" t="n">
         <v>26.9999324</v>
       </c>
-      <c r="T52" t="s">
-        <v>29</v>
+      <c r="T52" t="n">
+        <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB52" t="n">
         <v>8.92639032545044</v>
       </c>
-      <c r="V52" t="n">
+      <c r="AC52" t="n">
         <v>95.0023445317144</v>
       </c>
-      <c r="W52" t="n">
+      <c r="AD52" t="n">
         <v>19.983948777857</v>
       </c>
-      <c r="X52" t="n">
+      <c r="AE52" t="n">
         <v>19.9839487778572</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="AF52" t="n">
         <v>8.92639032545044</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="AG52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B53" t="n">
         <v>275.211316955463</v>
@@ -4969,31 +6082,52 @@
       <c r="S53" t="n">
         <v>51.000664</v>
       </c>
-      <c r="T53" t="s">
-        <v>29</v>
+      <c r="T53" t="n">
+        <v>0</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
       </c>
       <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
         <v>128.516834363193</v>
       </c>
-      <c r="W53" t="n">
+      <c r="AD53" t="n">
         <v>71.3825294828114</v>
       </c>
-      <c r="X53" t="n">
+      <c r="AE53" t="n">
         <v>71.3825294828114</v>
       </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>20.4388292789387</v>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>20.4388314674814</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B54" t="n">
         <v>430.130064239132</v>
@@ -5049,31 +6183,52 @@
       <c r="S54" t="n">
         <v>537.999295</v>
       </c>
-      <c r="T54" t="s">
-        <v>27</v>
+      <c r="T54" t="n">
+        <v>7</v>
       </c>
       <c r="U54" t="n">
+        <v>22</v>
+      </c>
+      <c r="V54" t="n">
+        <v>98</v>
+      </c>
+      <c r="W54" t="n">
+        <v>12</v>
+      </c>
+      <c r="X54" t="n">
+        <v>67.6153302394197</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>301.195561975597</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>36.8810892215017</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB54" t="n">
         <v>8.7580615057576</v>
       </c>
-      <c r="V54" t="n">
+      <c r="AC54" t="n">
         <v>13.0557543991887</v>
       </c>
-      <c r="W54" t="n">
+      <c r="AD54" t="n">
         <v>110.655432898667</v>
       </c>
-      <c r="X54" t="n">
+      <c r="AE54" t="n">
         <v>13.0557543991887</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AF54" t="n">
         <v>8.7580615057576</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="AG54" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B55" t="n">
         <v>389.125347191395</v>
@@ -5129,31 +6284,52 @@
       <c r="S55" t="n">
         <v>596.997856</v>
       </c>
-      <c r="T55" t="s">
-        <v>27</v>
+      <c r="T55" t="n">
+        <v>12</v>
       </c>
       <c r="U55" t="n">
+        <v>68</v>
+      </c>
+      <c r="V55" t="n">
+        <v>68</v>
+      </c>
+      <c r="W55" t="n">
+        <v>68</v>
+      </c>
+      <c r="X55" t="n">
+        <v>119.151918696338</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>119.151918696338</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>119.151918696338</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB55" t="n">
         <v>34.7708548218728</v>
       </c>
-      <c r="V55" t="n">
+      <c r="AC55" t="n">
         <v>42.486690526218</v>
       </c>
-      <c r="W55" t="n">
+      <c r="AD55" t="n">
         <v>106.64650160524</v>
       </c>
-      <c r="X55" t="n">
+      <c r="AE55" t="n">
         <v>42.486690526218</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AF55" t="n">
         <v>34.7708548218728</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="AG55" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B56" t="n">
         <v>378.238410644762</v>
@@ -5209,31 +6385,52 @@
       <c r="S56" t="n">
         <v>850.0012916</v>
       </c>
-      <c r="T56" t="s">
-        <v>27</v>
+      <c r="T56" t="n">
+        <v>180</v>
       </c>
       <c r="U56" t="n">
+        <v>865</v>
+      </c>
+      <c r="V56" t="n">
+        <v>967</v>
+      </c>
+      <c r="W56" t="n">
+        <v>585</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1993.63879413663</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2228.72683691343</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1348.29906886697</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB56" t="n">
         <v>46.6629041249914</v>
       </c>
-      <c r="V56" t="n">
+      <c r="AC56" t="n">
         <v>66.3551699930843</v>
       </c>
-      <c r="W56" t="n">
+      <c r="AD56" t="n">
         <v>119.348907424111</v>
       </c>
-      <c r="X56" t="n">
+      <c r="AE56" t="n">
         <v>66.3551699930843</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="AF56" t="n">
         <v>46.6629041249914</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="AG56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B57" t="n">
         <v>335.111548760014</v>
@@ -5289,31 +6486,52 @@
       <c r="S57" t="n">
         <v>631.9989819</v>
       </c>
-      <c r="T57" t="s">
-        <v>27</v>
+      <c r="T57" t="n">
+        <v>55</v>
       </c>
       <c r="U57" t="n">
+        <v>230</v>
+      </c>
+      <c r="V57" t="n">
+        <v>230</v>
+      </c>
+      <c r="W57" t="n">
+        <v>230</v>
+      </c>
+      <c r="X57" t="n">
+        <v>645.831578356218</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>645.831578356218</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>645.831578356218</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB57" t="n">
         <v>5.71248086016492</v>
       </c>
-      <c r="V57" t="n">
+      <c r="AC57" t="n">
         <v>42.175386727987</v>
       </c>
-      <c r="W57" t="n">
+      <c r="AD57" t="n">
         <v>154.514803910782</v>
       </c>
-      <c r="X57" t="n">
+      <c r="AE57" t="n">
         <v>42.175386727987</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AF57" t="n">
         <v>5.71248086016492</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="AG57" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B58" t="n">
         <v>1246.11869772911</v>
@@ -5369,31 +6587,52 @@
       <c r="S58" t="n">
         <v>2532.0028368</v>
       </c>
-      <c r="T58" t="s">
-        <v>27</v>
+      <c r="T58" t="n">
+        <v>493</v>
       </c>
       <c r="U58" t="n">
+        <v>2808</v>
+      </c>
+      <c r="V58" t="n">
+        <v>3207</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2581</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2217.5190321256</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>2532.61521938276</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2038.25378273368</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB58" t="n">
         <v>12.2496024647641</v>
       </c>
-      <c r="V58" t="n">
+      <c r="AC58" t="n">
         <v>92.5286864456849</v>
       </c>
-      <c r="W58" t="n">
+      <c r="AD58" t="n">
         <v>47.0094609749554</v>
       </c>
-      <c r="X58" t="n">
+      <c r="AE58" t="n">
         <v>47.0094609749554</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AF58" t="n">
         <v>12.2496024647641</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="AG58" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B59" t="n">
         <v>622.073948551661</v>
@@ -5449,31 +6688,52 @@
       <c r="S59" t="n">
         <v>489.00075</v>
       </c>
-      <c r="T59" t="s">
-        <v>29</v>
+      <c r="T59" t="n">
+        <v>5</v>
       </c>
       <c r="U59" t="n">
+        <v>292</v>
+      </c>
+      <c r="V59" t="n">
+        <v>295</v>
+      </c>
+      <c r="W59" t="n">
+        <v>292</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1065.8879357547</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>1076.83883920423</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>1065.8879357547</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB59" t="n">
         <v>34.6657531930918</v>
       </c>
-      <c r="V59" t="n">
+      <c r="AC59" t="n">
         <v>146.990216496331</v>
       </c>
-      <c r="W59" t="n">
+      <c r="AD59" t="n">
         <v>168.667027641795</v>
       </c>
-      <c r="X59" t="n">
+      <c r="AE59" t="n">
         <v>146.990216496331</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="AF59" t="n">
         <v>34.6657531930918</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="AG59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B60" t="n">
         <v>174.850686491101</v>
@@ -5529,31 +6789,52 @@
       <c r="S60" t="n">
         <v>7.0000125</v>
       </c>
-      <c r="T60" t="s">
-        <v>29</v>
+      <c r="T60" t="n">
+        <v>0</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
       </c>
       <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
         <v>115.421773767709</v>
       </c>
-      <c r="W60" t="n">
+      <c r="AD60" t="n">
         <v>43.7441916017336</v>
       </c>
-      <c r="X60" t="n">
+      <c r="AE60" t="n">
         <v>43.7441916017336</v>
       </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0.204563686083098</v>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>0.204563916023811</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B61" t="n">
         <v>981.501585907146</v>
@@ -5609,31 +6890,52 @@
       <c r="S61" t="n">
         <v>645.0006192</v>
       </c>
-      <c r="T61" t="s">
-        <v>27</v>
+      <c r="T61" t="n">
+        <v>58</v>
       </c>
       <c r="U61" t="n">
+        <v>370</v>
+      </c>
+      <c r="V61" t="n">
+        <v>370</v>
+      </c>
+      <c r="W61" t="n">
+        <v>370</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2560.9080841639</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>2560.9080841639</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2560.9080841639</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB61" t="n">
         <v>24.9705961067122</v>
       </c>
-      <c r="V61" t="n">
+      <c r="AC61" t="n">
         <v>68.408775535044</v>
       </c>
-      <c r="W61" t="n">
+      <c r="AD61" t="n">
         <v>13.7460952276488</v>
       </c>
-      <c r="X61" t="n">
+      <c r="AE61" t="n">
         <v>13.7460952276488</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="AF61" t="n">
         <v>13.7460952276488</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="AG61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B62" t="n">
         <v>259.642929709342</v>
@@ -5689,31 +6991,52 @@
       <c r="S62" t="n">
         <v>475.9992879</v>
       </c>
-      <c r="T62" t="s">
-        <v>27</v>
+      <c r="T62" t="n">
+        <v>23</v>
       </c>
       <c r="U62" t="n">
+        <v>62</v>
+      </c>
+      <c r="V62" t="n">
+        <v>66</v>
+      </c>
+      <c r="W62" t="n">
+        <v>62</v>
+      </c>
+      <c r="X62" t="n">
+        <v>201.868915442972</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>214.892716439293</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>201.868915442972</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB62" t="n">
         <v>63.1474826594813</v>
       </c>
-      <c r="V62" t="n">
+      <c r="AC62" t="n">
         <v>111.918659348985</v>
       </c>
-      <c r="W62" t="n">
+      <c r="AD62" t="n">
         <v>108.516248286972</v>
       </c>
-      <c r="X62" t="n">
+      <c r="AE62" t="n">
         <v>108.516248286972</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="AF62" t="n">
         <v>63.1474826594813</v>
       </c>
-      <c r="Z62" t="n">
-        <v>15.3519982098752</v>
+      <c r="AG62" t="n">
+        <v>15.3519946836183</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B63" t="n">
         <v>203.836237065018</v>
@@ -5769,31 +7092,52 @@
       <c r="S63" t="n">
         <v>277.9999664</v>
       </c>
-      <c r="T63" t="s">
-        <v>27</v>
+      <c r="T63" t="n">
+        <v>54</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="V63" t="n">
+        <v>169</v>
+      </c>
+      <c r="W63" t="n">
+        <v>149</v>
+      </c>
+      <c r="X63" t="n">
+        <v>495.741282938515</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>562.283737024221</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>495.741282938515</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
         <v>45.971606329512</v>
       </c>
-      <c r="W63" t="n">
+      <c r="AD63" t="n">
         <v>166.382259858979</v>
       </c>
-      <c r="X63" t="n">
+      <c r="AE63" t="n">
         <v>45.971606329512</v>
       </c>
-      <c r="Y63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" t="n">
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B64" t="n">
         <v>384.477397920206</v>
@@ -5849,31 +7193,52 @@
       <c r="S64" t="n">
         <v>280.9999188</v>
       </c>
-      <c r="T64" t="s">
-        <v>29</v>
+      <c r="T64" t="n">
+        <v>49</v>
       </c>
       <c r="U64" t="n">
+        <v>154</v>
+      </c>
+      <c r="V64" t="n">
+        <v>154</v>
+      </c>
+      <c r="W64" t="n">
+        <v>154</v>
+      </c>
+      <c r="X64" t="n">
+        <v>908.233073838169</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>908.233073838169</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>908.233073838169</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB64" t="n">
         <v>65.054212261194</v>
       </c>
-      <c r="V64" t="n">
+      <c r="AC64" t="n">
         <v>32.2859448365393</v>
       </c>
-      <c r="W64" t="n">
+      <c r="AD64" t="n">
         <v>59.9022759802811</v>
       </c>
-      <c r="X64" t="n">
+      <c r="AE64" t="n">
         <v>32.2859448365392</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="AF64" t="n">
         <v>32.2859448365392</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="AG64" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B65" t="n">
         <v>162.238242577243</v>
@@ -5929,31 +7294,52 @@
       <c r="S65" t="n">
         <v>363.0011522</v>
       </c>
-      <c r="T65" t="s">
-        <v>29</v>
+      <c r="T65" t="n">
+        <v>147</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="V65" t="n">
+        <v>349</v>
+      </c>
+      <c r="W65" t="n">
+        <v>327</v>
+      </c>
+      <c r="X65" t="n">
+        <v>1230.30281665315</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1230.30281665315</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>1152.74791130539</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
         <v>15.6665195478124</v>
       </c>
-      <c r="W65" t="n">
+      <c r="AD65" t="n">
         <v>153.075531897981</v>
       </c>
-      <c r="X65" t="n">
+      <c r="AE65" t="n">
         <v>15.6665195478124</v>
       </c>
-      <c r="Y65" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" t="n">
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B66" t="n">
         <v>549.464467332324</v>
@@ -6009,31 +7395,52 @@
       <c r="S66" t="n">
         <v>474.00061</v>
       </c>
-      <c r="T66" t="s">
-        <v>27</v>
+      <c r="T66" t="n">
+        <v>2</v>
       </c>
       <c r="U66" t="n">
+        <v>18</v>
+      </c>
+      <c r="V66" t="n">
+        <v>18</v>
+      </c>
+      <c r="W66" t="n">
+        <v>18</v>
+      </c>
+      <c r="X66" t="n">
+        <v>110.058086212168</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>110.058086212168</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>110.058086212168</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB66" t="n">
         <v>100.428046003833</v>
       </c>
-      <c r="V66" t="n">
+      <c r="AC66" t="n">
         <v>32.272172065065</v>
       </c>
-      <c r="W66" t="n">
+      <c r="AD66" t="n">
         <v>20.0538671415635</v>
       </c>
-      <c r="X66" t="n">
+      <c r="AE66" t="n">
         <v>20.0538671415625</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="AF66" t="n">
         <v>20.0538671415625</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="AG66" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B67" t="n">
         <v>369.502237272625</v>
@@ -6089,31 +7496,52 @@
       <c r="S67" t="n">
         <v>18.9998926</v>
       </c>
-      <c r="T67" t="s">
-        <v>29</v>
+      <c r="T67" t="n">
+        <v>2</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="V67" t="n">
+        <v>59</v>
+      </c>
+      <c r="W67" t="n">
+        <v>9</v>
+      </c>
+      <c r="X67" t="n">
+        <v>344.344578031983</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>344.344578031983</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>52.5271390218279</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
         <v>131.566112024136</v>
       </c>
-      <c r="W67" t="n">
+      <c r="AD67" t="n">
         <v>99.1808774160044</v>
       </c>
-      <c r="X67" t="n">
+      <c r="AE67" t="n">
         <v>99.1808774160042</v>
       </c>
-      <c r="Y67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>36.9927541063754</v>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>36.9927559438937</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B68" t="n">
         <v>839.161670694318</v>
@@ -6169,31 +7597,52 @@
       <c r="S68" t="n">
         <v>5208.9964835</v>
       </c>
-      <c r="T68" t="s">
-        <v>27</v>
+      <c r="T68" t="n">
+        <v>95</v>
       </c>
       <c r="U68" t="n">
+        <v>3254</v>
+      </c>
+      <c r="V68" t="n">
+        <v>3258</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1255</v>
+      </c>
+      <c r="X68" t="n">
+        <v>2891.33931030806</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2894.89350737052</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>1115.12932834561</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB68" t="n">
         <v>13.2048133449397</v>
       </c>
-      <c r="V68" t="n">
+      <c r="AC68" t="n">
         <v>155.184161882676</v>
       </c>
-      <c r="W68" t="n">
+      <c r="AD68" t="n">
         <v>211.882515471289</v>
       </c>
-      <c r="X68" t="n">
+      <c r="AE68" t="n">
         <v>155.184161882676</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="AF68" t="n">
         <v>13.2048133449397</v>
       </c>
-      <c r="Z68" t="n">
-        <v>1.59399464580788</v>
+      <c r="AG68" t="n">
+        <v>1.59399773858235</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B69" t="n">
         <v>612.839262678062</v>
@@ -6249,31 +7698,52 @@
       <c r="S69" t="n">
         <v>541.000746</v>
       </c>
-      <c r="T69" t="s">
-        <v>29</v>
+      <c r="T69" t="n">
+        <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB69" t="n">
         <v>4.88423907916392</v>
       </c>
-      <c r="V69" t="n">
+      <c r="AC69" t="n">
         <v>94.4025703166196</v>
       </c>
-      <c r="W69" t="n">
+      <c r="AD69" t="n">
         <v>163.306570659315</v>
       </c>
-      <c r="X69" t="n">
+      <c r="AE69" t="n">
         <v>94.4025703166196</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="AF69" t="n">
         <v>4.88423907916392</v>
       </c>
-      <c r="Z69" t="n">
-        <v>14.8695789346373</v>
+      <c r="AG69" t="n">
+        <v>14.8695764312526</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B70" t="n">
         <v>464.394062012098</v>
@@ -6329,31 +7799,52 @@
       <c r="S70" t="n">
         <v>464.000368</v>
       </c>
-      <c r="T70" t="s">
-        <v>27</v>
+      <c r="T70" t="n">
+        <v>50</v>
       </c>
       <c r="U70" t="n">
+        <v>243</v>
+      </c>
+      <c r="V70" t="n">
+        <v>243</v>
+      </c>
+      <c r="W70" t="n">
+        <v>233</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1229.75708502024</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>1229.75708502024</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>1179.14979757085</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB70" t="n">
         <v>26.1646404927228</v>
       </c>
-      <c r="V70" t="n">
+      <c r="AC70" t="n">
         <v>116.372519600556</v>
       </c>
-      <c r="W70" t="n">
+      <c r="AD70" t="n">
         <v>90.3605859885676</v>
       </c>
-      <c r="X70" t="n">
+      <c r="AE70" t="n">
         <v>90.3605859885674</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="AF70" t="n">
         <v>26.1646404927228</v>
       </c>
-      <c r="Z70" t="n">
-        <v>26.3796485537592</v>
+      <c r="AG70" t="n">
+        <v>26.3796452720002</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B71" t="n">
         <v>637.955008045496</v>
@@ -6409,31 +7900,52 @@
       <c r="S71" t="n">
         <v>2014.0001838</v>
       </c>
-      <c r="T71" t="s">
-        <v>27</v>
+      <c r="T71" t="n">
+        <v>194</v>
       </c>
       <c r="U71" t="n">
+        <v>1273</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1316</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1222</v>
+      </c>
+      <c r="X71" t="n">
+        <v>5792.15579215579</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>5987.80598780599</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>5560.10556010556</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB71" t="n">
         <v>94.9913636390876</v>
       </c>
-      <c r="V71" t="n">
+      <c r="AC71" t="n">
         <v>2.41984776544902</v>
       </c>
-      <c r="W71" t="n">
+      <c r="AD71" t="n">
         <v>15.3710044738084</v>
       </c>
-      <c r="X71" t="n">
+      <c r="AE71" t="n">
         <v>2.41984776544902</v>
       </c>
-      <c r="Y71" t="n">
+      <c r="AF71" t="n">
         <v>2.41984776544902</v>
       </c>
-      <c r="Z71" t="n">
+      <c r="AG71" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B72" t="n">
         <v>321.148261001312</v>
@@ -6489,31 +8001,52 @@
       <c r="S72" t="n">
         <v>252.0001806</v>
       </c>
-      <c r="T72" t="s">
-        <v>27</v>
+      <c r="T72" t="n">
+        <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB72" t="n">
         <v>129.114135010524</v>
       </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
         <v>9.66902923255692</v>
       </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>12.3124281536922</v>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>12.3124252678406</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B73" t="n">
         <v>963.750100946136</v>
@@ -6569,31 +8102,52 @@
       <c r="S73" t="n">
         <v>1542.0017444</v>
       </c>
-      <c r="T73" t="s">
-        <v>27</v>
+      <c r="T73" t="n">
+        <v>60</v>
       </c>
       <c r="U73" t="n">
+        <v>746</v>
+      </c>
+      <c r="V73" t="n">
+        <v>770</v>
+      </c>
+      <c r="W73" t="n">
+        <v>599</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1237.00399621934</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>1276.80037143284</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>993.251198036712</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB73" t="n">
         <v>14.3161676747165</v>
       </c>
-      <c r="V73" t="n">
+      <c r="AC73" t="n">
         <v>167.124536265521</v>
       </c>
-      <c r="W73" t="n">
+      <c r="AD73" t="n">
         <v>203.521129676426</v>
       </c>
-      <c r="X73" t="n">
+      <c r="AE73" t="n">
         <v>167.124536265521</v>
       </c>
-      <c r="Y73" t="n">
+      <c r="AF73" t="n">
         <v>14.3161676747165</v>
       </c>
-      <c r="Z73" t="n">
+      <c r="AG73" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B74" t="n">
         <v>31.7473542247513</v>
@@ -6649,31 +8203,52 @@
       <c r="S74" t="n">
         <v>1551.0006606</v>
       </c>
-      <c r="T74" t="s">
-        <v>27</v>
+      <c r="T74" t="n">
+        <v>0</v>
       </c>
       <c r="U74" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB74" t="n">
         <v>97.8152166537519</v>
       </c>
-      <c r="V74" t="n">
+      <c r="AC74" t="n">
         <v>62.0952193396157</v>
       </c>
-      <c r="W74" t="n">
+      <c r="AD74" t="n">
         <v>53.945007466199</v>
       </c>
-      <c r="X74" t="n">
+      <c r="AE74" t="n">
         <v>53.9450074661988</v>
       </c>
-      <c r="Y74" t="n">
+      <c r="AF74" t="n">
         <v>53.9450074661988</v>
       </c>
-      <c r="Z74" t="n">
+      <c r="AG74" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="B75" t="n">
         <v>40.7232747923128</v>
@@ -6729,31 +8304,52 @@
       <c r="S75" t="n">
         <v>3150.9933936</v>
       </c>
-      <c r="T75" t="s">
-        <v>27</v>
+      <c r="T75" t="n">
+        <v>18</v>
       </c>
       <c r="U75" t="n">
+        <v>141</v>
+      </c>
+      <c r="V75" t="n">
+        <v>153</v>
+      </c>
+      <c r="W75" t="n">
+        <v>130</v>
+      </c>
+      <c r="X75" t="n">
+        <v>103.208994554079</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>111.992738771447</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>95.1572290214909</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB75" t="n">
         <v>88.5529891941859</v>
       </c>
-      <c r="V75" t="n">
+      <c r="AC75" t="n">
         <v>70.2202753925215</v>
       </c>
-      <c r="W75" t="n">
+      <c r="AD75" t="n">
         <v>56.6307323557078</v>
       </c>
-      <c r="X75" t="n">
+      <c r="AE75" t="n">
         <v>56.6307323557076</v>
       </c>
-      <c r="Y75" t="n">
+      <c r="AF75" t="n">
         <v>56.6307323557076</v>
       </c>
-      <c r="Z75" t="n">
+      <c r="AG75" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B76" t="n">
         <v>72.9129960665233</v>
@@ -6809,31 +8405,52 @@
       <c r="S76" t="n">
         <v>1924.0022993</v>
       </c>
-      <c r="T76" t="s">
-        <v>27</v>
+      <c r="T76" t="n">
+        <v>731</v>
       </c>
       <c r="U76" t="n">
+        <v>3885</v>
+      </c>
+      <c r="V76" t="n">
+        <v>4923</v>
+      </c>
+      <c r="W76" t="n">
+        <v>3535</v>
+      </c>
+      <c r="X76" t="n">
+        <v>4085.64607893658</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>5177.25499269106</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>3717.56985560896</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB76" t="n">
         <v>90.9185939718103</v>
       </c>
-      <c r="V76" t="n">
+      <c r="AC76" t="n">
         <v>60.4068723851582</v>
       </c>
-      <c r="W76" t="n">
+      <c r="AD76" t="n">
         <v>44.048809330892</v>
       </c>
-      <c r="X76" t="n">
+      <c r="AE76" t="n">
         <v>44.0488093308918</v>
       </c>
-      <c r="Y76" t="n">
+      <c r="AF76" t="n">
         <v>44.0488093308918</v>
       </c>
-      <c r="Z76" t="n">
+      <c r="AG76" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B77" t="n">
         <v>130.135721221302</v>
@@ -6889,31 +8506,52 @@
       <c r="S77" t="n">
         <v>1152.0004368</v>
       </c>
-      <c r="T77" t="s">
-        <v>29</v>
+      <c r="T77" t="n">
+        <v>0</v>
       </c>
       <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB77" t="n">
         <v>98.7151046787356</v>
       </c>
-      <c r="V77" t="n">
+      <c r="AC77" t="n">
         <v>51.4549240236687</v>
       </c>
-      <c r="W77" t="n">
+      <c r="AD77" t="n">
         <v>47.0122971904285</v>
       </c>
-      <c r="X77" t="n">
+      <c r="AE77" t="n">
         <v>47.0122971904284</v>
       </c>
-      <c r="Y77" t="n">
+      <c r="AF77" t="n">
         <v>47.0122971904284</v>
       </c>
-      <c r="Z77" t="n">
+      <c r="AG77" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B78" t="n">
         <v>70.4847992002451</v>
@@ -6969,31 +8607,52 @@
       <c r="S78" t="n">
         <v>710.9994031</v>
       </c>
-      <c r="T78" t="s">
+      <c r="T78" t="n">
+        <v>4</v>
+      </c>
+      <c r="U78" t="n">
         <v>27</v>
       </c>
-      <c r="U78" t="n">
+      <c r="V78" t="n">
+        <v>30</v>
+      </c>
+      <c r="W78" t="n">
+        <v>7</v>
+      </c>
+      <c r="X78" t="n">
+        <v>109.546800827687</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>121.718667586319</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>28.4010224368077</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB78" t="n">
         <v>91.7408825616456</v>
       </c>
-      <c r="V78" t="n">
+      <c r="AC78" t="n">
         <v>63.8298391812008</v>
       </c>
-      <c r="W78" t="n">
+      <c r="AD78" t="n">
         <v>58.3205258954239</v>
       </c>
-      <c r="X78" t="n">
+      <c r="AE78" t="n">
         <v>58.3205258954237</v>
       </c>
-      <c r="Y78" t="n">
+      <c r="AF78" t="n">
         <v>58.3205258954237</v>
       </c>
-      <c r="Z78" t="n">
-        <v>4.03407727375236</v>
+      <c r="AG78" t="n">
+        <v>4.03408098955466</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B79" t="n">
         <v>287.724225141255</v>
@@ -7049,31 +8708,52 @@
       <c r="S79" t="n">
         <v>167.0006254</v>
       </c>
-      <c r="T79" t="s">
-        <v>27</v>
+      <c r="T79" t="n">
+        <v>1</v>
       </c>
       <c r="U79" t="n">
+        <v>8</v>
+      </c>
+      <c r="V79" t="n">
+        <v>8</v>
+      </c>
+      <c r="W79" t="n">
+        <v>8</v>
+      </c>
+      <c r="X79" t="n">
+        <v>41.198887630034</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>41.198887630034</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>41.198887630034</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB79" t="n">
         <v>61.3335295153581</v>
       </c>
-      <c r="V79" t="n">
+      <c r="AC79" t="n">
         <v>127.818494168139</v>
       </c>
-      <c r="W79" t="n">
+      <c r="AD79" t="n">
         <v>146.726747299151</v>
       </c>
-      <c r="X79" t="n">
+      <c r="AE79" t="n">
         <v>127.818494168139</v>
       </c>
-      <c r="Y79" t="n">
+      <c r="AF79" t="n">
         <v>61.3335295153581</v>
       </c>
-      <c r="Z79" t="n">
+      <c r="AG79" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B80" t="n">
         <v>688.121336720116</v>
@@ -7129,31 +8809,52 @@
       <c r="S80" t="n">
         <v>405.9993102</v>
       </c>
-      <c r="T80" t="s">
-        <v>27</v>
+      <c r="T80" t="n">
+        <v>3</v>
       </c>
       <c r="U80" t="n">
+        <v>3</v>
+      </c>
+      <c r="V80" t="n">
+        <v>3</v>
+      </c>
+      <c r="W80" t="n">
+        <v>3</v>
+      </c>
+      <c r="X80" t="n">
+        <v>20.1572263656521</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>20.1572263656521</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>20.1572263656521</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB80" t="n">
         <v>85.6949124610119</v>
       </c>
-      <c r="V80" t="n">
+      <c r="AC80" t="n">
         <v>15.5998355533037</v>
       </c>
-      <c r="W80" t="n">
+      <c r="AD80" t="n">
         <v>32.5311773351287</v>
       </c>
-      <c r="X80" t="n">
+      <c r="AE80" t="n">
         <v>15.5998355533037</v>
       </c>
-      <c r="Y80" t="n">
+      <c r="AF80" t="n">
         <v>15.5998355533037</v>
       </c>
-      <c r="Z80" t="n">
-        <v>0.452971442975501</v>
+      <c r="AG80" t="n">
+        <v>0.452973047771236</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B81" t="n">
         <v>472.225751824517</v>
@@ -7209,31 +8910,52 @@
       <c r="S81" t="n">
         <v>127.999872</v>
       </c>
-      <c r="T81" t="s">
-        <v>29</v>
+      <c r="T81" t="n">
+        <v>0</v>
       </c>
       <c r="U81" t="n">
         <v>0</v>
       </c>
       <c r="V81" t="n">
+        <v>0</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" t="n">
         <v>94.6050401777627</v>
       </c>
-      <c r="W81" t="n">
+      <c r="AD81" t="n">
         <v>187.939143109488</v>
       </c>
-      <c r="X81" t="n">
+      <c r="AE81" t="n">
         <v>94.6050401777627</v>
       </c>
-      <c r="Y81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>29.9134819687162</v>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>29.9134807408449</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B82" t="n">
         <v>515.234744915733</v>
@@ -7289,31 +9011,52 @@
       <c r="S82" t="n">
         <v>7710.9991308</v>
       </c>
-      <c r="T82" t="s">
-        <v>29</v>
+      <c r="T82" t="n">
+        <v>363</v>
       </c>
       <c r="U82" t="n">
+        <v>15317</v>
+      </c>
+      <c r="V82" t="n">
+        <v>15503</v>
+      </c>
+      <c r="W82" t="n">
+        <v>15278</v>
+      </c>
+      <c r="X82" t="n">
+        <v>41774.3958981072</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>42281.6778486882</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>41668.0303278241</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB82" t="n">
         <v>78.8222479984853</v>
       </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="n">
         <v>45.4372836214434</v>
       </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>30.3358347683355</v>
+      <c r="AE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>30.3358356804222</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B83" t="n">
         <v>224.855291358604</v>
@@ -7369,31 +9112,52 @@
       <c r="S83" t="n">
         <v>298.9988352</v>
       </c>
-      <c r="T83" t="s">
-        <v>29</v>
+      <c r="T83" t="n">
+        <v>1</v>
       </c>
       <c r="U83" t="n">
+        <v>3</v>
+      </c>
+      <c r="V83" t="n">
+        <v>3</v>
+      </c>
+      <c r="W83" t="n">
+        <v>3</v>
+      </c>
+      <c r="X83" t="n">
+        <v>7.33568075117371</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>7.33568075117371</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>7.33568075117371</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB83" t="n">
         <v>22.1008579327384</v>
       </c>
-      <c r="V83" t="n">
+      <c r="AC83" t="n">
         <v>33.5889301163639</v>
       </c>
-      <c r="W83" t="n">
+      <c r="AD83" t="n">
         <v>121.165312768626</v>
       </c>
-      <c r="X83" t="n">
+      <c r="AE83" t="n">
         <v>33.5889301163639</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="AF83" t="n">
         <v>22.1008579327384</v>
       </c>
-      <c r="Z83" t="n">
+      <c r="AG83" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B84" t="n">
         <v>524.924563312052</v>
@@ -7449,31 +9213,52 @@
       <c r="S84" t="n">
         <v>187.9999797</v>
       </c>
-      <c r="T84" t="s">
-        <v>27</v>
+      <c r="T84" t="n">
+        <v>17</v>
       </c>
       <c r="U84" t="n">
+        <v>53</v>
+      </c>
+      <c r="V84" t="n">
+        <v>53</v>
+      </c>
+      <c r="W84" t="n">
+        <v>53</v>
+      </c>
+      <c r="X84" t="n">
+        <v>283.710722124083</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>283.710722124083</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>283.710722124083</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB84" t="n">
         <v>4.86509088680042</v>
       </c>
-      <c r="V84" t="n">
+      <c r="AC84" t="n">
         <v>88.7735172536607</v>
       </c>
-      <c r="W84" t="n">
+      <c r="AD84" t="n">
         <v>24.6416417131483</v>
       </c>
-      <c r="X84" t="n">
+      <c r="AE84" t="n">
         <v>24.6416417131483</v>
       </c>
-      <c r="Y84" t="n">
+      <c r="AF84" t="n">
         <v>4.86509088680042</v>
       </c>
-      <c r="Z84" t="n">
+      <c r="AG84" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B85" t="n">
         <v>834.824383403903</v>
@@ -7529,31 +9314,52 @@
       <c r="S85" t="n">
         <v>737.0002582</v>
       </c>
-      <c r="T85" t="s">
-        <v>27</v>
+      <c r="T85" t="n">
+        <v>199</v>
       </c>
       <c r="U85" t="n">
+        <v>585</v>
+      </c>
+      <c r="V85" t="n">
+        <v>653</v>
+      </c>
+      <c r="W85" t="n">
+        <v>515</v>
+      </c>
+      <c r="X85" t="n">
+        <v>977.378287165436</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1090.9880709727</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>860.427039128546</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB85" t="n">
         <v>33.6862140323773</v>
       </c>
-      <c r="V85" t="n">
+      <c r="AC85" t="n">
         <v>90.84201125669</v>
       </c>
-      <c r="W85" t="n">
+      <c r="AD85" t="n">
         <v>128.862260976704</v>
       </c>
-      <c r="X85" t="n">
+      <c r="AE85" t="n">
         <v>90.84201125669</v>
       </c>
-      <c r="Y85" t="n">
+      <c r="AF85" t="n">
         <v>33.6862140323773</v>
       </c>
-      <c r="Z85" t="n">
+      <c r="AG85" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B86" t="n">
         <v>209.901074976234</v>
@@ -7609,31 +9415,52 @@
       <c r="S86" t="n">
         <v>756.001968</v>
       </c>
-      <c r="T86" t="s">
-        <v>29</v>
+      <c r="T86" t="n">
+        <v>252</v>
       </c>
       <c r="U86" t="n">
+        <v>524</v>
+      </c>
+      <c r="V86" t="n">
+        <v>548</v>
+      </c>
+      <c r="W86" t="n">
+        <v>524</v>
+      </c>
+      <c r="X86" t="n">
+        <v>1080.85808580858</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1130.36303630363</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1080.85808580858</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB86" t="n">
         <v>36.6527310551573</v>
       </c>
-      <c r="V86" t="n">
+      <c r="AC86" t="n">
         <v>76.9341905066008</v>
       </c>
-      <c r="W86" t="n">
+      <c r="AD86" t="n">
         <v>133.874761645333</v>
       </c>
-      <c r="X86" t="n">
+      <c r="AE86" t="n">
         <v>76.9341905066008</v>
       </c>
-      <c r="Y86" t="n">
+      <c r="AF86" t="n">
         <v>36.6527310551573</v>
       </c>
-      <c r="Z86" t="n">
+      <c r="AG86" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B87" t="n">
         <v>958.793044004204</v>
@@ -7689,31 +9516,52 @@
       <c r="S87" t="n">
         <v>82.9988922</v>
       </c>
-      <c r="T87" t="s">
-        <v>29</v>
+      <c r="T87" t="n">
+        <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V87" t="n">
+        <v>12</v>
+      </c>
+      <c r="W87" t="n">
+        <v>12</v>
+      </c>
+      <c r="X87" t="n">
+        <v>39.9880035989203</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>39.9880035989203</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>39.9880035989203</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
         <v>134.700439716881</v>
       </c>
-      <c r="W87" t="n">
+      <c r="AD87" t="n">
         <v>104.265088888487</v>
       </c>
-      <c r="X87" t="n">
+      <c r="AE87" t="n">
         <v>104.265088888487</v>
       </c>
-      <c r="Y87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>19.9214021596825</v>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>19.9214000128638</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B88" t="n">
         <v>548.708138909663</v>
@@ -7769,31 +9617,52 @@
       <c r="S88" t="n">
         <v>1287.9986579</v>
       </c>
-      <c r="T88" t="s">
-        <v>27</v>
+      <c r="T88" t="n">
+        <v>385</v>
       </c>
       <c r="U88" t="n">
+        <v>1867</v>
+      </c>
+      <c r="V88" t="n">
+        <v>2302</v>
+      </c>
+      <c r="W88" t="n">
+        <v>1837</v>
+      </c>
+      <c r="X88" t="n">
+        <v>2638.98115821166</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>3253.8482197125</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>2596.57653328056</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB88" t="n">
         <v>68.4329536436013</v>
       </c>
-      <c r="V88" t="n">
+      <c r="AC88" t="n">
         <v>102.92406829184</v>
       </c>
-      <c r="W88" t="n">
+      <c r="AD88" t="n">
         <v>119.869158442375</v>
       </c>
-      <c r="X88" t="n">
+      <c r="AE88" t="n">
         <v>102.92406829184</v>
       </c>
-      <c r="Y88" t="n">
+      <c r="AF88" t="n">
         <v>68.4329536436013</v>
       </c>
-      <c r="Z88" t="n">
+      <c r="AG88" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B89" t="n">
         <v>1119.79808959912</v>
@@ -7849,31 +9718,52 @@
       <c r="S89" t="n">
         <v>345.000978</v>
       </c>
-      <c r="T89" t="s">
-        <v>27</v>
+      <c r="T89" t="n">
+        <v>35</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="V89" t="n">
+        <v>109</v>
+      </c>
+      <c r="W89" t="n">
+        <v>109</v>
+      </c>
+      <c r="X89" t="n">
+        <v>351.658278487547</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>351.658278487547</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>351.658278487547</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" t="n">
         <v>96.1884291901985</v>
       </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z89" t="n">
+      <c r="AD89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B90" t="n">
         <v>489.35354131407</v>
@@ -7929,31 +9819,52 @@
       <c r="S90" t="n">
         <v>351.9996464</v>
       </c>
-      <c r="T90" t="s">
-        <v>27</v>
+      <c r="T90" t="n">
+        <v>94</v>
       </c>
       <c r="U90" t="n">
+        <v>378</v>
+      </c>
+      <c r="V90" t="n">
+        <v>552</v>
+      </c>
+      <c r="W90" t="n">
+        <v>348</v>
+      </c>
+      <c r="X90" t="n">
+        <v>5406.95179516521</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>7895.8661135746</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>4977.82863681877</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB90" t="n">
         <v>72.9735545660637</v>
       </c>
-      <c r="V90" t="n">
+      <c r="AC90" t="n">
         <v>46.6920801910042</v>
       </c>
-      <c r="W90" t="n">
+      <c r="AD90" t="n">
         <v>28.5179376478762</v>
       </c>
-      <c r="X90" t="n">
+      <c r="AE90" t="n">
         <v>28.517937647876</v>
       </c>
-      <c r="Y90" t="n">
+      <c r="AF90" t="n">
         <v>28.517937647876</v>
       </c>
-      <c r="Z90" t="n">
+      <c r="AG90" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B91" t="n">
         <v>317.162097519447</v>
@@ -8009,31 +9920,52 @@
       <c r="S91" t="n">
         <v>1158.0014876</v>
       </c>
-      <c r="T91" t="s">
-        <v>27</v>
+      <c r="T91" t="n">
+        <v>185</v>
       </c>
       <c r="U91" t="n">
+        <v>860</v>
+      </c>
+      <c r="V91" t="n">
+        <v>1167</v>
+      </c>
+      <c r="W91" t="n">
+        <v>732</v>
+      </c>
+      <c r="X91" t="n">
+        <v>653.406069078697</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>886.656840249814</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>556.154933215822</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB91" t="n">
         <v>27.4458037478199</v>
       </c>
-      <c r="V91" t="n">
+      <c r="AC91" t="n">
         <v>17.9061403524382</v>
       </c>
-      <c r="W91" t="n">
+      <c r="AD91" t="n">
         <v>104.757739420606</v>
       </c>
-      <c r="X91" t="n">
+      <c r="AE91" t="n">
         <v>17.9061403524382</v>
       </c>
-      <c r="Y91" t="n">
+      <c r="AF91" t="n">
         <v>17.9061403524382</v>
       </c>
-      <c r="Z91" t="n">
+      <c r="AG91" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B92" t="n">
         <v>191.658172338384</v>
@@ -8089,31 +10021,52 @@
       <c r="S92" t="n">
         <v>563.0009958</v>
       </c>
-      <c r="T92" t="s">
-        <v>27</v>
+      <c r="T92" t="n">
+        <v>5</v>
       </c>
       <c r="U92" t="n">
+        <v>11</v>
+      </c>
+      <c r="V92" t="n">
+        <v>211</v>
+      </c>
+      <c r="W92" t="n">
+        <v>11</v>
+      </c>
+      <c r="X92" t="n">
+        <v>42.9905811544925</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>824.637511236175</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>42.9905811544925</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB92" t="n">
         <v>10.402787687945</v>
       </c>
-      <c r="V92" t="n">
+      <c r="AC92" t="n">
         <v>7.12006734725357</v>
       </c>
-      <c r="W92" t="n">
+      <c r="AD92" t="n">
         <v>113.518570257891</v>
       </c>
-      <c r="X92" t="n">
+      <c r="AE92" t="n">
         <v>7.12006734725306</v>
       </c>
-      <c r="Y92" t="n">
+      <c r="AF92" t="n">
         <v>7.12006734725306</v>
       </c>
-      <c r="Z92" t="n">
+      <c r="AG92" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B93" t="n">
         <v>489.853140840578</v>
@@ -8169,31 +10122,52 @@
       <c r="S93" t="n">
         <v>354.0001914</v>
       </c>
-      <c r="T93" t="s">
-        <v>27</v>
+      <c r="T93" t="n">
+        <v>67</v>
       </c>
       <c r="U93" t="n">
+        <v>291</v>
+      </c>
+      <c r="V93" t="n">
+        <v>291</v>
+      </c>
+      <c r="W93" t="n">
+        <v>226</v>
+      </c>
+      <c r="X93" t="n">
+        <v>1310.6336981489</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>1310.6336981489</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>1017.88046660361</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB93" t="n">
         <v>73.2410540795095</v>
       </c>
-      <c r="V93" t="n">
+      <c r="AC93" t="n">
         <v>49.2861331058029</v>
       </c>
-      <c r="W93" t="n">
+      <c r="AD93" t="n">
         <v>70.4286671412754</v>
       </c>
-      <c r="X93" t="n">
+      <c r="AE93" t="n">
         <v>49.2861331058029</v>
       </c>
-      <c r="Y93" t="n">
+      <c r="AF93" t="n">
         <v>49.2861331058029</v>
       </c>
-      <c r="Z93" t="n">
-        <v>10.3208809528193</v>
+      <c r="AG93" t="n">
+        <v>10.3208769810978</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B94" t="n">
         <v>350.811901830945</v>
@@ -8249,31 +10223,52 @@
       <c r="S94" t="n">
         <v>1077.0005388</v>
       </c>
-      <c r="T94" t="s">
-        <v>29</v>
+      <c r="T94" t="n">
+        <v>302</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1128</v>
       </c>
       <c r="V94" t="n">
+        <v>1192</v>
+      </c>
+      <c r="W94" t="n">
+        <v>1101</v>
+      </c>
+      <c r="X94" t="n">
+        <v>2132.0027217056</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>2252.96741513571</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>2080.97074166478</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" t="n">
         <v>221.589485713694</v>
       </c>
-      <c r="W94" t="n">
+      <c r="AD94" t="n">
         <v>284.032242270425</v>
       </c>
-      <c r="X94" t="n">
+      <c r="AE94" t="n">
         <v>221.589485713694</v>
       </c>
-      <c r="Y94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="n">
-        <v>14.1445258474751</v>
+      <c r="AF94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>14.1445224260749</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B95" t="n">
         <v>293.000411490812</v>
@@ -8329,31 +10324,52 @@
       <c r="S95" t="n">
         <v>663.997752</v>
       </c>
-      <c r="T95" t="s">
-        <v>29</v>
+      <c r="T95" t="n">
+        <v>8</v>
       </c>
       <c r="U95" t="n">
+        <v>10</v>
+      </c>
+      <c r="V95" t="n">
+        <v>11</v>
+      </c>
+      <c r="W95" t="n">
+        <v>10</v>
+      </c>
+      <c r="X95" t="n">
+        <v>21.6637781629116</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>23.8301559792028</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>21.6637781629116</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB95" t="n">
         <v>80.7164106042104</v>
       </c>
-      <c r="V95" t="n">
+      <c r="AC95" t="n">
         <v>73.824748960079</v>
       </c>
-      <c r="W95" t="n">
+      <c r="AD95" t="n">
         <v>67.3728494057921</v>
       </c>
-      <c r="X95" t="n">
+      <c r="AE95" t="n">
         <v>67.372849405792</v>
       </c>
-      <c r="Y95" t="n">
+      <c r="AF95" t="n">
         <v>67.372849405792</v>
       </c>
-      <c r="Z95" t="n">
-        <v>10.6886250857726</v>
+      <c r="AG95" t="n">
+        <v>10.6886256390109</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B96" t="n">
         <v>151.100880525903</v>
@@ -8409,31 +10425,52 @@
       <c r="S96" t="n">
         <v>998.0013147</v>
       </c>
-      <c r="T96" t="s">
-        <v>27</v>
+      <c r="T96" t="n">
+        <v>287</v>
       </c>
       <c r="U96" t="n">
+        <v>1563</v>
+      </c>
+      <c r="V96" t="n">
+        <v>1620</v>
+      </c>
+      <c r="W96" t="n">
+        <v>1553</v>
+      </c>
+      <c r="X96" t="n">
+        <v>5610.39520442227</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>5814.99694892135</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>5574.50016152769</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB96" t="n">
         <v>72.5248161398812</v>
       </c>
-      <c r="V96" t="n">
+      <c r="AC96" t="n">
         <v>101.483065996233</v>
       </c>
-      <c r="W96" t="n">
+      <c r="AD96" t="n">
         <v>109.137026944843</v>
       </c>
-      <c r="X96" t="n">
+      <c r="AE96" t="n">
         <v>101.483065996233</v>
       </c>
-      <c r="Y96" t="n">
+      <c r="AF96" t="n">
         <v>72.5248161398812</v>
       </c>
-      <c r="Z96" t="n">
-        <v>18.0129403009271</v>
+      <c r="AG96" t="n">
+        <v>18.0129376008853</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B97" t="n">
         <v>469.5121911515</v>
@@ -8489,31 +10526,52 @@
       <c r="S97" t="n">
         <v>1760.0003372</v>
       </c>
-      <c r="T97" t="s">
-        <v>27</v>
+      <c r="T97" t="n">
+        <v>29</v>
       </c>
       <c r="U97" t="n">
+        <v>135</v>
+      </c>
+      <c r="V97" t="n">
+        <v>135</v>
+      </c>
+      <c r="W97" t="n">
+        <v>85</v>
+      </c>
+      <c r="X97" t="n">
+        <v>636.822491626963</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>636.822491626963</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>400.962309542903</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB97" t="n">
         <v>102.506383989577</v>
       </c>
-      <c r="V97" t="n">
-        <v>0</v>
-      </c>
-      <c r="W97" t="n">
+      <c r="AC97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" t="n">
         <v>17.3050554302496</v>
       </c>
-      <c r="X97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y97" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z97" t="n">
-        <v>15.0060494008255</v>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>15.0060477660355</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B98" t="n">
         <v>483.15716226466</v>
@@ -8569,31 +10627,52 @@
       <c r="S98" t="n">
         <v>2934.0007872</v>
       </c>
-      <c r="T98" t="s">
-        <v>27</v>
+      <c r="T98" t="n">
+        <v>14</v>
       </c>
       <c r="U98" t="n">
+        <v>104</v>
+      </c>
+      <c r="V98" t="n">
+        <v>534</v>
+      </c>
+      <c r="W98" t="n">
+        <v>104</v>
+      </c>
+      <c r="X98" t="n">
+        <v>306.405043898415</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1573.27205232455</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>306.405043898415</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB98" t="n">
         <v>61.8402583346309</v>
       </c>
-      <c r="V98" t="n">
+      <c r="AC98" t="n">
         <v>3.59053460873044</v>
       </c>
-      <c r="W98" t="n">
+      <c r="AD98" t="n">
         <v>51.917085914026</v>
       </c>
-      <c r="X98" t="n">
+      <c r="AE98" t="n">
         <v>3.59053460873044</v>
       </c>
-      <c r="Y98" t="n">
+      <c r="AF98" t="n">
         <v>3.59053460873044</v>
       </c>
-      <c r="Z98" t="n">
+      <c r="AG98" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B99" t="n">
         <v>553.850181436845</v>
@@ -8649,31 +10728,52 @@
       <c r="S99" t="n">
         <v>892.9988588</v>
       </c>
-      <c r="T99" t="s">
-        <v>27</v>
+      <c r="T99" t="n">
+        <v>142</v>
       </c>
       <c r="U99" t="n">
+        <v>503</v>
+      </c>
+      <c r="V99" t="n">
+        <v>567</v>
+      </c>
+      <c r="W99" t="n">
+        <v>503</v>
+      </c>
+      <c r="X99" t="n">
+        <v>879.924427961654</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>991.883003288783</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>879.924427961654</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB99" t="n">
         <v>58.9414874805371</v>
       </c>
-      <c r="V99" t="n">
+      <c r="AC99" t="n">
         <v>47.155985869668</v>
       </c>
-      <c r="W99" t="n">
+      <c r="AD99" t="n">
         <v>93.0522926108538</v>
       </c>
-      <c r="X99" t="n">
+      <c r="AE99" t="n">
         <v>47.155985869668</v>
       </c>
-      <c r="Y99" t="n">
+      <c r="AF99" t="n">
         <v>47.155985869668</v>
       </c>
-      <c r="Z99" t="n">
-        <v>7.99726604192458</v>
+      <c r="AG99" t="n">
+        <v>7.9972641918535</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B100" t="n">
         <v>503.326228760109</v>
@@ -8729,31 +10829,52 @@
       <c r="S100" t="n">
         <v>1429.995559</v>
       </c>
-      <c r="T100" t="s">
-        <v>27</v>
+      <c r="T100" t="n">
+        <v>92</v>
       </c>
       <c r="U100" t="n">
+        <v>260</v>
+      </c>
+      <c r="V100" t="n">
+        <v>879</v>
+      </c>
+      <c r="W100" t="n">
+        <v>254</v>
+      </c>
+      <c r="X100" t="n">
+        <v>178.673282159473</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>604.053134685294</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>174.550052571177</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB100" t="n">
         <v>73.8755673580021</v>
       </c>
-      <c r="V100" t="n">
+      <c r="AC100" t="n">
         <v>82.7437325589725</v>
       </c>
-      <c r="W100" t="n">
+      <c r="AD100" t="n">
         <v>99.3696428075682</v>
       </c>
-      <c r="X100" t="n">
+      <c r="AE100" t="n">
         <v>82.7437325589725</v>
       </c>
-      <c r="Y100" t="n">
+      <c r="AF100" t="n">
         <v>73.8755673580021</v>
       </c>
-      <c r="Z100" t="n">
-        <v>2.78569277041679</v>
+      <c r="AG100" t="n">
+        <v>2.78569037549652</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B101" t="n">
         <v>471.142764766818</v>
@@ -8809,31 +10930,52 @@
       <c r="S101" t="n">
         <v>4126.9975815</v>
       </c>
-      <c r="T101" t="s">
-        <v>27</v>
+      <c r="T101" t="n">
+        <v>217</v>
       </c>
       <c r="U101" t="n">
+        <v>1567</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1726</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1567</v>
+      </c>
+      <c r="X101" t="n">
+        <v>1927.54781966911</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>2123.13180392398</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>1927.54781966911</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB101" t="n">
         <v>29.255698653921</v>
       </c>
-      <c r="V101" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" t="n">
+      <c r="AC101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD101" t="n">
         <v>78.7226734552482</v>
       </c>
-      <c r="X101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z101" t="n">
+      <c r="AE101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B102" t="n">
         <v>234.740784938321</v>
@@ -8889,31 +11031,52 @@
       <c r="S102" t="n">
         <v>287.0003936</v>
       </c>
-      <c r="T102" t="s">
-        <v>27</v>
+      <c r="T102" t="n">
+        <v>4</v>
       </c>
       <c r="U102" t="n">
+        <v>63</v>
+      </c>
+      <c r="V102" t="n">
+        <v>63</v>
+      </c>
+      <c r="W102" t="n">
+        <v>63</v>
+      </c>
+      <c r="X102" t="n">
+        <v>703.439035283609</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>703.439035283609</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>703.439035283609</v>
+      </c>
+      <c r="AA102" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102" t="n">
         <v>110.361626884814</v>
       </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>4.86246757862822</v>
+      <c r="AC102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>4.86246494876177</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B103" t="n">
         <v>289.506629696803</v>
@@ -8969,31 +11132,52 @@
       <c r="S103" t="n">
         <v>238.9989276</v>
       </c>
-      <c r="T103" t="s">
-        <v>27</v>
+      <c r="T103" t="n">
+        <v>35</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="V103" t="n">
+        <v>83</v>
+      </c>
+      <c r="W103" t="n">
+        <v>83</v>
+      </c>
+      <c r="X103" t="n">
+        <v>297.683093034933</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>297.683093034933</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>297.683093034933</v>
+      </c>
+      <c r="AA103" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC103" t="n">
         <v>112.361569092821</v>
       </c>
-      <c r="W103" t="n">
+      <c r="AD103" t="n">
         <v>51.9446536062566</v>
       </c>
-      <c r="X103" t="n">
+      <c r="AE103" t="n">
         <v>51.9446536062566</v>
       </c>
-      <c r="Y103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z103" t="n">
-        <v>3.11989121053369</v>
+      <c r="AF103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>3.11989326998354</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="B104" t="n">
         <v>365.092384392457</v>
@@ -9049,31 +11233,52 @@
       <c r="S104" t="n">
         <v>242.9995328</v>
       </c>
-      <c r="T104" t="s">
-        <v>29</v>
+      <c r="T104" t="n">
+        <v>1</v>
       </c>
       <c r="U104" t="n">
+        <v>3</v>
+      </c>
+      <c r="V104" t="n">
+        <v>3</v>
+      </c>
+      <c r="W104" t="n">
+        <v>3</v>
+      </c>
+      <c r="X104" t="n">
+        <v>16.0316357612355</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>16.0316357612355</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>16.0316357612355</v>
+      </c>
+      <c r="AA104" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB104" t="n">
         <v>34.1218746843303</v>
       </c>
-      <c r="V104" t="n">
+      <c r="AC104" t="n">
         <v>110.124512828022</v>
       </c>
-      <c r="W104" t="n">
+      <c r="AD104" t="n">
         <v>164.552236397084</v>
       </c>
-      <c r="X104" t="n">
+      <c r="AE104" t="n">
         <v>110.124512828022</v>
       </c>
-      <c r="Y104" t="n">
+      <c r="AF104" t="n">
         <v>34.1218746843303</v>
       </c>
-      <c r="Z104" t="n">
-        <v>19.3131783171693</v>
+      <c r="AG104" t="n">
+        <v>19.3131745224598</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B105" t="n">
         <v>181.959061051478</v>
@@ -9129,31 +11334,52 @@
       <c r="S105" t="n">
         <v>35.0001015</v>
       </c>
-      <c r="T105" t="s">
-        <v>29</v>
+      <c r="T105" t="n">
+        <v>0</v>
       </c>
       <c r="U105" t="n">
+        <v>0</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB105" t="n">
         <v>5.5812036993974</v>
       </c>
-      <c r="V105" t="n">
+      <c r="AC105" t="n">
         <v>116.231086964071</v>
       </c>
-      <c r="W105" t="n">
+      <c r="AD105" t="n">
         <v>62.4816568433886</v>
       </c>
-      <c r="X105" t="n">
+      <c r="AE105" t="n">
         <v>62.4816568433886</v>
       </c>
-      <c r="Y105" t="n">
+      <c r="AF105" t="n">
         <v>5.5812036993974</v>
       </c>
-      <c r="Z105" t="n">
-        <v>9.44858226736763</v>
+      <c r="AG105" t="n">
+        <v>9.4485812020695</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B106" t="n">
         <v>254.669690006658</v>
@@ -9209,31 +11435,52 @@
       <c r="S106" t="n">
         <v>188.9999378</v>
       </c>
-      <c r="T106" t="s">
-        <v>29</v>
+      <c r="T106" t="n">
+        <v>0</v>
       </c>
       <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB106" t="n">
         <v>52.4767991710442</v>
       </c>
-      <c r="V106" t="n">
+      <c r="AC106" t="n">
         <v>6.65773906243044</v>
       </c>
-      <c r="W106" t="n">
+      <c r="AD106" t="n">
         <v>73.9691953117172</v>
       </c>
-      <c r="X106" t="n">
+      <c r="AE106" t="n">
         <v>6.65773906243054</v>
       </c>
-      <c r="Y106" t="n">
+      <c r="AF106" t="n">
         <v>6.65773906243054</v>
       </c>
-      <c r="Z106" t="n">
+      <c r="AG106" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B107" t="n">
         <v>477.214081946568</v>
@@ -9289,31 +11536,52 @@
       <c r="S107" t="n">
         <v>189.9999261</v>
       </c>
-      <c r="T107" t="s">
-        <v>29</v>
+      <c r="T107" t="n">
+        <v>0</v>
       </c>
       <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB107" t="n">
         <v>36.8754328478688</v>
       </c>
-      <c r="V107" t="n">
+      <c r="AC107" t="n">
         <v>147.368650522223</v>
       </c>
-      <c r="W107" t="n">
+      <c r="AD107" t="n">
         <v>147.216923828273</v>
       </c>
-      <c r="X107" t="n">
+      <c r="AE107" t="n">
         <v>147.216923828273</v>
       </c>
-      <c r="Y107" t="n">
+      <c r="AF107" t="n">
         <v>36.8754328478688</v>
       </c>
-      <c r="Z107" t="n">
-        <v>0.0787665579337847</v>
+      <c r="AG107" t="n">
+        <v>0.0787669302425168</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B108" t="n">
         <v>401.380057723587</v>
@@ -9369,31 +11637,52 @@
       <c r="S108" t="n">
         <v>50.944012</v>
       </c>
-      <c r="T108" t="s">
-        <v>29</v>
+      <c r="T108" t="n">
+        <v>0</v>
       </c>
       <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB108" t="n">
         <v>8.96381536413674</v>
       </c>
-      <c r="V108" t="n">
+      <c r="AC108" t="n">
         <v>119.005229541096</v>
       </c>
-      <c r="W108" t="n">
+      <c r="AD108" t="n">
         <v>71.8301704965085</v>
       </c>
-      <c r="X108" t="n">
+      <c r="AE108" t="n">
         <v>71.8301704965085</v>
       </c>
-      <c r="Y108" t="n">
+      <c r="AF108" t="n">
         <v>8.96381536413674</v>
       </c>
-      <c r="Z108" t="n">
-        <v>18.7073036840034</v>
+      <c r="AG108" t="n">
+        <v>18.7073068698466</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="B109" t="n">
         <v>215.999582280115</v>
@@ -9449,31 +11738,52 @@
       <c r="S109" t="n">
         <v>330.9997716</v>
       </c>
-      <c r="T109" t="s">
-        <v>27</v>
+      <c r="T109" t="n">
+        <v>105</v>
       </c>
       <c r="U109" t="n">
+        <v>439</v>
+      </c>
+      <c r="V109" t="n">
+        <v>543</v>
+      </c>
+      <c r="W109" t="n">
+        <v>437</v>
+      </c>
+      <c r="X109" t="n">
+        <v>1911.52137943046</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>2364.36471305408</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>1902.81285378385</v>
+      </c>
+      <c r="AA109" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB109" t="n">
         <v>66.2866202500579</v>
       </c>
-      <c r="V109" t="n">
+      <c r="AC109" t="n">
         <v>79.6213827702462</v>
       </c>
-      <c r="W109" t="n">
+      <c r="AD109" t="n">
         <v>112.722639557362</v>
       </c>
-      <c r="X109" t="n">
+      <c r="AE109" t="n">
         <v>79.6213827702462</v>
       </c>
-      <c r="Y109" t="n">
+      <c r="AF109" t="n">
         <v>66.2866202500579</v>
       </c>
-      <c r="Z109" t="n">
+      <c r="AG109" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B110" t="n">
         <v>254.687934354389</v>
@@ -9529,27 +11839,91 @@
       <c r="S110" t="n">
         <v>369.0018531</v>
       </c>
-      <c r="T110" t="s">
-        <v>29</v>
+      <c r="T110" t="n">
+        <v>1</v>
       </c>
       <c r="U110" t="n">
+        <v>1</v>
+      </c>
+      <c r="V110" t="n">
+        <v>1</v>
+      </c>
+      <c r="W110" t="n">
+        <v>1</v>
+      </c>
+      <c r="X110" t="n">
+        <v>1.8253837869412</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>1.8253837869412</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>1.8253837869412</v>
+      </c>
+      <c r="AA110" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB110" t="n">
         <v>40.6043856884861</v>
       </c>
-      <c r="V110" t="n">
+      <c r="AC110" t="n">
         <v>20.5556105865153</v>
       </c>
-      <c r="W110" t="n">
+      <c r="AD110" t="n">
         <v>89.3181719362026</v>
       </c>
-      <c r="X110" t="n">
+      <c r="AE110" t="n">
         <v>20.5556105865153</v>
       </c>
-      <c r="Y110" t="n">
+      <c r="AF110" t="n">
         <v>20.5556105865153</v>
       </c>
-      <c r="Z110" t="n">
-        <v>1.5871365361478</v>
-      </c>
+      <c r="AG110" t="n">
+        <v>1.58714215670637</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
+      <c r="M111"/>
+      <c r="N111"/>
+      <c r="O111"/>
+      <c r="P111"/>
+      <c r="Q111"/>
+      <c r="R111"/>
+      <c r="S111"/>
+      <c r="T111" t="n">
+        <v>2</v>
+      </c>
+      <c r="U111" t="n">
+        <v>30</v>
+      </c>
+      <c r="V111" t="n">
+        <v>39</v>
+      </c>
+      <c r="W111" t="n">
+        <v>30</v>
+      </c>
+      <c r="X111"/>
+      <c r="Y111"/>
+      <c r="Z111"/>
+      <c r="AA111"/>
+      <c r="AB111"/>
+      <c r="AC111"/>
+      <c r="AD111"/>
+      <c r="AE111"/>
+      <c r="AF111"/>
+      <c r="AG111"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
